--- a/140_tests/results/OpenBSE_Std140_AE_Output.xlsx
+++ b/140_tests/results/OpenBSE_Std140_AE_Output.xlsx
@@ -2638,13 +2638,27 @@
           <t>Dry bulb temperature (°C)</t>
         </is>
       </c>
-      <c r="S61" s="86" t="n"/>
-      <c r="T61" s="28" t="n"/>
-      <c r="U61" s="28" t="n"/>
-      <c r="V61" s="28" t="n"/>
-      <c r="W61" s="28" t="n"/>
-      <c r="X61" s="28" t="n"/>
-      <c r="Y61" s="29" t="n"/>
+      <c r="S61" s="86" t="n">
+        <v>-29</v>
+      </c>
+      <c r="T61" s="28" t="n">
+        <v>4.4314</v>
+      </c>
+      <c r="U61" s="28" t="n">
+        <v>29.0808</v>
+      </c>
+      <c r="V61" s="28" t="n">
+        <v>29.0808</v>
+      </c>
+      <c r="W61" s="28" t="n">
+        <v>29.6868</v>
+      </c>
+      <c r="X61" s="28" t="n">
+        <v>21.1445</v>
+      </c>
+      <c r="Y61" s="29" t="n">
+        <v>21.1445</v>
+      </c>
     </row>
     <row r="62" ht="15" customHeight="1">
       <c r="B62" s="34" t="inlineStr">
@@ -2682,13 +2696,27 @@
           <t>Humidity ratio (g/gda)</t>
         </is>
       </c>
-      <c r="S62" s="87" t="n"/>
-      <c r="T62" s="32" t="n"/>
-      <c r="U62" s="32" t="n"/>
-      <c r="V62" s="32" t="n"/>
-      <c r="W62" s="32" t="n"/>
-      <c r="X62" s="32" t="n"/>
-      <c r="Y62" s="33" t="n"/>
+      <c r="S62" s="87" t="n">
+        <v>0.000259</v>
+      </c>
+      <c r="T62" s="32" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="U62" s="32" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="V62" s="32" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="W62" s="32" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="X62" s="32" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="Y62" s="33" t="n">
+        <v>0.0023</v>
+      </c>
     </row>
     <row r="63" ht="15" customHeight="1">
       <c r="B63" s="36" t="inlineStr">
@@ -2726,13 +2754,27 @@
           <t>Specific volume (L/kgda)</t>
         </is>
       </c>
-      <c r="S63" s="87" t="n"/>
-      <c r="T63" s="32" t="n"/>
-      <c r="U63" s="32" t="n"/>
-      <c r="V63" s="32" t="n"/>
-      <c r="W63" s="32" t="n"/>
-      <c r="X63" s="32" t="n"/>
-      <c r="Y63" s="33" t="n"/>
+      <c r="S63" s="87" t="n">
+        <v>691.9367</v>
+      </c>
+      <c r="T63" s="32" t="n">
+        <v>788.3789</v>
+      </c>
+      <c r="U63" s="32" t="n">
+        <v>858.3875</v>
+      </c>
+      <c r="V63" s="32" t="n">
+        <v>858.3875</v>
+      </c>
+      <c r="W63" s="32" t="n">
+        <v>860.1086</v>
+      </c>
+      <c r="X63" s="32" t="n">
+        <v>836.7854</v>
+      </c>
+      <c r="Y63" s="33" t="n">
+        <v>836.7854</v>
+      </c>
     </row>
     <row r="64" ht="15" customHeight="1">
       <c r="Q64" s="22" t="n"/>
@@ -2741,13 +2783,27 @@
           <t>Enthalpy (J/gda)</t>
         </is>
       </c>
-      <c r="S64" s="87" t="n"/>
-      <c r="T64" s="32" t="n"/>
-      <c r="U64" s="32" t="n"/>
-      <c r="V64" s="32" t="n"/>
-      <c r="W64" s="32" t="n"/>
-      <c r="X64" s="32" t="n"/>
-      <c r="Y64" s="33" t="n"/>
+      <c r="S64" s="87" t="n">
+        <v>-28.5402</v>
+      </c>
+      <c r="T64" s="32" t="n">
+        <v>8.472799999999999</v>
+      </c>
+      <c r="U64" s="32" t="n">
+        <v>33.3434</v>
+      </c>
+      <c r="V64" s="32" t="n">
+        <v>33.3434</v>
+      </c>
+      <c r="W64" s="32" t="n">
+        <v>33.9549</v>
+      </c>
+      <c r="X64" s="32" t="n">
+        <v>27.1141</v>
+      </c>
+      <c r="Y64" s="33" t="n">
+        <v>27.1141</v>
+      </c>
     </row>
     <row r="65" ht="15" customHeight="1">
       <c r="Q65" s="38" t="n"/>
@@ -2756,11 +2812,21 @@
           <t>Mass flow rate (kgda/s)</t>
         </is>
       </c>
-      <c r="S65" s="88" t="n"/>
-      <c r="T65" s="39" t="n"/>
-      <c r="U65" s="39" t="n"/>
-      <c r="V65" s="39" t="n"/>
-      <c r="W65" s="39" t="n"/>
+      <c r="S65" s="88" t="n">
+        <v>0.113292</v>
+      </c>
+      <c r="T65" s="39" t="n">
+        <v>0.339457</v>
+      </c>
+      <c r="U65" s="39" t="n">
+        <v>0.339457</v>
+      </c>
+      <c r="V65" s="39" t="n">
+        <v>0.339457</v>
+      </c>
+      <c r="W65" s="39" t="n">
+        <v>0.339457</v>
+      </c>
       <c r="X65" s="39" t="inlineStr">
         <is>
           <t>n/a*</t>
@@ -2780,13 +2846,27 @@
           <t>Dry bulb temperature (°C)</t>
         </is>
       </c>
-      <c r="S66" s="86" t="n"/>
-      <c r="T66" s="28" t="n"/>
-      <c r="U66" s="28" t="n"/>
-      <c r="V66" s="28" t="n"/>
-      <c r="W66" s="28" t="n"/>
-      <c r="X66" s="28" t="n"/>
-      <c r="Y66" s="29" t="n"/>
+      <c r="S66" s="86" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="T66" s="28" t="n">
+        <v>20.702</v>
+      </c>
+      <c r="U66" s="28" t="n">
+        <v>20.702</v>
+      </c>
+      <c r="V66" s="28" t="n">
+        <v>18.4696</v>
+      </c>
+      <c r="W66" s="28" t="n">
+        <v>19.0539</v>
+      </c>
+      <c r="X66" s="28" t="n">
+        <v>23.3026</v>
+      </c>
+      <c r="Y66" s="29" t="n">
+        <v>23.3026</v>
+      </c>
     </row>
     <row r="67" ht="15" customHeight="1">
       <c r="B67" s="41" t="n"/>
@@ -2796,13 +2876,27 @@
           <t>Humidity ratio (g/gda)</t>
         </is>
       </c>
-      <c r="S67" s="87" t="n"/>
-      <c r="T67" s="32" t="n"/>
-      <c r="U67" s="32" t="n"/>
-      <c r="V67" s="32" t="n"/>
-      <c r="W67" s="32" t="n"/>
-      <c r="X67" s="32" t="n"/>
-      <c r="Y67" s="33" t="n"/>
+      <c r="S67" s="87" t="n">
+        <v>0.002992</v>
+      </c>
+      <c r="T67" s="32" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="U67" s="32" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="V67" s="32" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="W67" s="32" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="X67" s="32" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="Y67" s="33" t="n">
+        <v>0.005</v>
+      </c>
     </row>
     <row r="68" ht="15" customHeight="1">
       <c r="B68" s="41" t="n"/>
@@ -2812,13 +2906,27 @@
           <t>Specific volume (L/kgda)</t>
         </is>
       </c>
-      <c r="S68" s="87" t="n"/>
-      <c r="T68" s="32" t="n"/>
-      <c r="U68" s="32" t="n"/>
-      <c r="V68" s="32" t="n"/>
-      <c r="W68" s="32" t="n"/>
-      <c r="X68" s="32" t="n"/>
-      <c r="Y68" s="33" t="n"/>
+      <c r="S68" s="87" t="n">
+        <v>821.6458</v>
+      </c>
+      <c r="T68" s="32" t="n">
+        <v>838.2041</v>
+      </c>
+      <c r="U68" s="32" t="n">
+        <v>838.2041</v>
+      </c>
+      <c r="V68" s="32" t="n">
+        <v>831.8362</v>
+      </c>
+      <c r="W68" s="32" t="n">
+        <v>833.5029</v>
+      </c>
+      <c r="X68" s="32" t="n">
+        <v>846.5674</v>
+      </c>
+      <c r="Y68" s="33" t="n">
+        <v>846.5674</v>
+      </c>
     </row>
     <row r="69" ht="15" customHeight="1">
       <c r="B69" s="41" t="n"/>
@@ -2828,13 +2936,27 @@
           <t>Enthalpy (J/gda)</t>
         </is>
       </c>
-      <c r="S69" s="87" t="n"/>
-      <c r="T69" s="32" t="n"/>
-      <c r="U69" s="32" t="n"/>
-      <c r="V69" s="32" t="n"/>
-      <c r="W69" s="32" t="n"/>
-      <c r="X69" s="32" t="n"/>
-      <c r="Y69" s="33" t="n"/>
+      <c r="S69" s="87" t="n">
+        <v>23.1623</v>
+      </c>
+      <c r="T69" s="32" t="n">
+        <v>31.7461</v>
+      </c>
+      <c r="U69" s="32" t="n">
+        <v>31.7461</v>
+      </c>
+      <c r="V69" s="32" t="n">
+        <v>29.4824</v>
+      </c>
+      <c r="W69" s="32" t="n">
+        <v>30.0749</v>
+      </c>
+      <c r="X69" s="32" t="n">
+        <v>36.1641</v>
+      </c>
+      <c r="Y69" s="33" t="n">
+        <v>36.1641</v>
+      </c>
     </row>
     <row r="70" ht="15" customHeight="1">
       <c r="B70" s="41" t="n"/>
@@ -2844,11 +2966,21 @@
           <t>Mass flow rate (kgda/s)</t>
         </is>
       </c>
-      <c r="S70" s="88" t="n"/>
-      <c r="T70" s="39" t="n"/>
-      <c r="U70" s="39" t="n"/>
-      <c r="V70" s="39" t="n"/>
-      <c r="W70" s="39" t="n"/>
+      <c r="S70" s="88" t="n">
+        <v>0.112984</v>
+      </c>
+      <c r="T70" s="39" t="n">
+        <v>0.338544</v>
+      </c>
+      <c r="U70" s="39" t="n">
+        <v>0.338544</v>
+      </c>
+      <c r="V70" s="39" t="n">
+        <v>0.338544</v>
+      </c>
+      <c r="W70" s="39" t="n">
+        <v>0.338544</v>
+      </c>
       <c r="X70" s="39" t="inlineStr">
         <is>
           <t>n/a*</t>
@@ -2868,13 +3000,27 @@
           <t>Dry bulb temperature (°C)</t>
         </is>
       </c>
-      <c r="S71" s="86" t="n"/>
-      <c r="T71" s="28" t="n"/>
-      <c r="U71" s="28" t="n"/>
-      <c r="V71" s="28" t="n"/>
-      <c r="W71" s="28" t="n"/>
-      <c r="X71" s="28" t="n"/>
-      <c r="Y71" s="29" t="n"/>
+      <c r="S71" s="86" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="T71" s="28" t="n">
+        <v>24.8015</v>
+      </c>
+      <c r="U71" s="28" t="n">
+        <v>24.8015</v>
+      </c>
+      <c r="V71" s="28" t="n">
+        <v>14.7711</v>
+      </c>
+      <c r="W71" s="28" t="n">
+        <v>15.3471</v>
+      </c>
+      <c r="X71" s="28" t="n">
+        <v>23.7524</v>
+      </c>
+      <c r="Y71" s="29" t="n">
+        <v>23.7524</v>
+      </c>
     </row>
     <row r="72" ht="15" customHeight="1">
       <c r="B72" s="41" t="n"/>
@@ -2884,13 +3030,27 @@
           <t>Humidity ratio (g/gda)</t>
         </is>
       </c>
-      <c r="S72" s="87" t="n"/>
-      <c r="T72" s="32" t="n"/>
-      <c r="U72" s="32" t="n"/>
-      <c r="V72" s="32" t="n"/>
-      <c r="W72" s="32" t="n"/>
-      <c r="X72" s="32" t="n"/>
-      <c r="Y72" s="33" t="n"/>
+      <c r="S72" s="87" t="n">
+        <v>0.01698</v>
+      </c>
+      <c r="T72" s="32" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="U72" s="32" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="V72" s="32" t="n">
+        <v>0.0105</v>
+      </c>
+      <c r="W72" s="32" t="n">
+        <v>0.0105</v>
+      </c>
+      <c r="X72" s="32" t="n">
+        <v>0.0112</v>
+      </c>
+      <c r="Y72" s="33" t="n">
+        <v>0.0112</v>
+      </c>
     </row>
     <row r="73" ht="15" customHeight="1">
       <c r="B73" s="2" t="n"/>
@@ -2900,13 +3060,27 @@
           <t>Specific volume (L/kgda)</t>
         </is>
       </c>
-      <c r="S73" s="87" t="n"/>
-      <c r="T73" s="32" t="n"/>
-      <c r="U73" s="32" t="n"/>
-      <c r="V73" s="32" t="n"/>
-      <c r="W73" s="32" t="n"/>
-      <c r="X73" s="32" t="n"/>
-      <c r="Y73" s="33" t="n"/>
+      <c r="S73" s="87" t="n">
+        <v>873.2133</v>
+      </c>
+      <c r="T73" s="32" t="n">
+        <v>861.7048</v>
+      </c>
+      <c r="U73" s="32" t="n">
+        <v>861.7048</v>
+      </c>
+      <c r="V73" s="32" t="n">
+        <v>829.4173</v>
+      </c>
+      <c r="W73" s="32" t="n">
+        <v>831.0766</v>
+      </c>
+      <c r="X73" s="32" t="n">
+        <v>856.2365</v>
+      </c>
+      <c r="Y73" s="33" t="n">
+        <v>856.2365</v>
+      </c>
     </row>
     <row r="74" ht="15" customHeight="1">
       <c r="B74" s="2" t="n"/>
@@ -2916,13 +3090,27 @@
           <t>Enthalpy (J/gda)</t>
         </is>
       </c>
-      <c r="S74" s="87" t="n"/>
-      <c r="T74" s="32" t="n"/>
-      <c r="U74" s="32" t="n"/>
-      <c r="V74" s="32" t="n"/>
-      <c r="W74" s="32" t="n"/>
-      <c r="X74" s="32" t="n"/>
-      <c r="Y74" s="33" t="n"/>
+      <c r="S74" s="87" t="n">
+        <v>70.378</v>
+      </c>
+      <c r="T74" s="32" t="n">
+        <v>58.063</v>
+      </c>
+      <c r="U74" s="32" t="n">
+        <v>58.063</v>
+      </c>
+      <c r="V74" s="32" t="n">
+        <v>41.4087</v>
+      </c>
+      <c r="W74" s="32" t="n">
+        <v>41.9994</v>
+      </c>
+      <c r="X74" s="32" t="n">
+        <v>52.4009</v>
+      </c>
+      <c r="Y74" s="33" t="n">
+        <v>52.4009</v>
+      </c>
     </row>
     <row r="75" ht="15" customHeight="1">
       <c r="B75" s="2" t="n"/>
@@ -2932,11 +3120,21 @@
           <t>Mass flow rate (kgda/s)</t>
         </is>
       </c>
-      <c r="S75" s="88" t="n"/>
-      <c r="T75" s="39" t="n"/>
-      <c r="U75" s="39" t="n"/>
-      <c r="V75" s="39" t="n"/>
-      <c r="W75" s="39" t="n"/>
+      <c r="S75" s="88" t="n">
+        <v>0.11143</v>
+      </c>
+      <c r="T75" s="39" t="n">
+        <v>0.335637</v>
+      </c>
+      <c r="U75" s="39" t="n">
+        <v>0.335637</v>
+      </c>
+      <c r="V75" s="39" t="n">
+        <v>0.336467</v>
+      </c>
+      <c r="W75" s="39" t="n">
+        <v>0.336467</v>
+      </c>
       <c r="X75" s="39" t="inlineStr">
         <is>
           <t>n/a*</t>
@@ -3405,14 +3603,30 @@
           <t>Dry bulb temperature (°C)</t>
         </is>
       </c>
-      <c r="S89" s="92" t="n"/>
-      <c r="T89" s="28" t="n"/>
-      <c r="U89" s="28" t="n"/>
-      <c r="V89" s="28" t="n"/>
-      <c r="W89" s="28" t="n"/>
-      <c r="X89" s="28" t="n"/>
-      <c r="Y89" s="28" t="n"/>
-      <c r="Z89" s="29" t="n"/>
+      <c r="S89" s="92" t="n">
+        <v>-29</v>
+      </c>
+      <c r="T89" s="28" t="n">
+        <v>4.6278</v>
+      </c>
+      <c r="U89" s="28" t="n">
+        <v>29.0808</v>
+      </c>
+      <c r="V89" s="28" t="n">
+        <v>29.0808</v>
+      </c>
+      <c r="W89" s="28" t="n">
+        <v>29.6868</v>
+      </c>
+      <c r="X89" s="28" t="n">
+        <v>21.1445</v>
+      </c>
+      <c r="Y89" s="28" t="n">
+        <v>21.1445</v>
+      </c>
+      <c r="Z89" s="29" t="n">
+        <v>21.4395</v>
+      </c>
     </row>
     <row r="90" ht="15" customHeight="1">
       <c r="B90" s="34" t="inlineStr">
@@ -3450,14 +3664,30 @@
           <t>Humidity ratio (g/gda)</t>
         </is>
       </c>
-      <c r="S90" s="93" t="n"/>
-      <c r="T90" s="32" t="n"/>
-      <c r="U90" s="32" t="n"/>
-      <c r="V90" s="32" t="n"/>
-      <c r="W90" s="32" t="n"/>
-      <c r="X90" s="32" t="n"/>
-      <c r="Y90" s="32" t="n"/>
-      <c r="Z90" s="33" t="n"/>
+      <c r="S90" s="93" t="n">
+        <v>0.000259</v>
+      </c>
+      <c r="T90" s="32" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="U90" s="32" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="V90" s="32" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="W90" s="32" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="X90" s="32" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="Y90" s="32" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="Z90" s="33" t="n">
+        <v>0.0023</v>
+      </c>
     </row>
     <row r="91" ht="15" customHeight="1">
       <c r="B91" s="34" t="inlineStr">
@@ -3495,14 +3725,30 @@
           <t>Specific volume (L/kgda)</t>
         </is>
       </c>
-      <c r="S91" s="93" t="n"/>
-      <c r="T91" s="32" t="n"/>
-      <c r="U91" s="32" t="n"/>
-      <c r="V91" s="32" t="n"/>
-      <c r="W91" s="32" t="n"/>
-      <c r="X91" s="32" t="n"/>
-      <c r="Y91" s="32" t="n"/>
-      <c r="Z91" s="33" t="n"/>
+      <c r="S91" s="93" t="n">
+        <v>691.9367</v>
+      </c>
+      <c r="T91" s="32" t="n">
+        <v>788.9367999999999</v>
+      </c>
+      <c r="U91" s="32" t="n">
+        <v>858.3875</v>
+      </c>
+      <c r="V91" s="32" t="n">
+        <v>858.3875</v>
+      </c>
+      <c r="W91" s="32" t="n">
+        <v>860.1086</v>
+      </c>
+      <c r="X91" s="32" t="n">
+        <v>836.7854</v>
+      </c>
+      <c r="Y91" s="32" t="n">
+        <v>836.7854</v>
+      </c>
+      <c r="Z91" s="33" t="n">
+        <v>837.6241</v>
+      </c>
     </row>
     <row r="92" ht="15" customHeight="1">
       <c r="B92" s="34" t="inlineStr">
@@ -3540,14 +3786,30 @@
           <t>Enthalpy (J/gda)</t>
         </is>
       </c>
-      <c r="S92" s="93" t="n"/>
-      <c r="T92" s="32" t="n"/>
-      <c r="U92" s="32" t="n"/>
-      <c r="V92" s="32" t="n"/>
-      <c r="W92" s="32" t="n"/>
-      <c r="X92" s="32" t="n"/>
-      <c r="Y92" s="32" t="n"/>
-      <c r="Z92" s="33" t="n"/>
+      <c r="S92" s="93" t="n">
+        <v>-28.5402</v>
+      </c>
+      <c r="T92" s="32" t="n">
+        <v>8.6709</v>
+      </c>
+      <c r="U92" s="32" t="n">
+        <v>33.3434</v>
+      </c>
+      <c r="V92" s="32" t="n">
+        <v>33.3434</v>
+      </c>
+      <c r="W92" s="32" t="n">
+        <v>33.9549</v>
+      </c>
+      <c r="X92" s="32" t="n">
+        <v>27.1141</v>
+      </c>
+      <c r="Y92" s="32" t="n">
+        <v>27.1141</v>
+      </c>
+      <c r="Z92" s="33" t="n">
+        <v>27.4122</v>
+      </c>
     </row>
     <row r="93" ht="15" customHeight="1">
       <c r="B93" s="34" t="inlineStr">
@@ -3585,18 +3847,32 @@
           <t>Mass flow rate (kgda/s)</t>
         </is>
       </c>
-      <c r="S93" s="94" t="n"/>
-      <c r="T93" s="39" t="n"/>
-      <c r="U93" s="39" t="n"/>
-      <c r="V93" s="39" t="n"/>
-      <c r="W93" s="39" t="n"/>
+      <c r="S93" s="94" t="n">
+        <v>0.113294</v>
+      </c>
+      <c r="T93" s="39" t="n">
+        <v>0.339457</v>
+      </c>
+      <c r="U93" s="39" t="n">
+        <v>0.339457</v>
+      </c>
+      <c r="V93" s="39" t="n">
+        <v>0.339457</v>
+      </c>
+      <c r="W93" s="39" t="n">
+        <v>0.339457</v>
+      </c>
       <c r="X93" s="39" t="inlineStr">
         <is>
           <t>n/a*</t>
         </is>
       </c>
-      <c r="Y93" s="39" t="n"/>
-      <c r="Z93" s="40" t="n"/>
+      <c r="Y93" s="39" t="n">
+        <v>0.226156</v>
+      </c>
+      <c r="Z93" s="40" t="n">
+        <v>0.226156</v>
+      </c>
     </row>
     <row r="94" ht="15" customHeight="1">
       <c r="B94" s="34" t="inlineStr">
@@ -3638,14 +3914,30 @@
           <t>Dry bulb temperature (°C)</t>
         </is>
       </c>
-      <c r="S94" s="92" t="n"/>
-      <c r="T94" s="28" t="n"/>
-      <c r="U94" s="28" t="n"/>
-      <c r="V94" s="28" t="n"/>
-      <c r="W94" s="28" t="n"/>
-      <c r="X94" s="28" t="n"/>
-      <c r="Y94" s="28" t="n"/>
-      <c r="Z94" s="29" t="n"/>
+      <c r="S94" s="92" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="T94" s="28" t="n">
+        <v>20.8985</v>
+      </c>
+      <c r="U94" s="28" t="n">
+        <v>20.8985</v>
+      </c>
+      <c r="V94" s="28" t="n">
+        <v>18.4696</v>
+      </c>
+      <c r="W94" s="28" t="n">
+        <v>19.0539</v>
+      </c>
+      <c r="X94" s="28" t="n">
+        <v>23.3026</v>
+      </c>
+      <c r="Y94" s="28" t="n">
+        <v>23.3026</v>
+      </c>
+      <c r="Z94" s="29" t="n">
+        <v>23.5976</v>
+      </c>
     </row>
     <row r="95" ht="15" customHeight="1">
       <c r="B95" s="36" t="inlineStr">
@@ -3683,14 +3975,30 @@
           <t>Humidity ratio (g/gda)</t>
         </is>
       </c>
-      <c r="S95" s="93" t="n"/>
-      <c r="T95" s="32" t="n"/>
-      <c r="U95" s="32" t="n"/>
-      <c r="V95" s="32" t="n"/>
-      <c r="W95" s="32" t="n"/>
-      <c r="X95" s="32" t="n"/>
-      <c r="Y95" s="32" t="n"/>
-      <c r="Z95" s="33" t="n"/>
+      <c r="S95" s="93" t="n">
+        <v>0.002992</v>
+      </c>
+      <c r="T95" s="32" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="U95" s="32" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="V95" s="32" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="W95" s="32" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="X95" s="32" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="Y95" s="32" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="Z95" s="33" t="n">
+        <v>0.005</v>
+      </c>
     </row>
     <row r="96" ht="15" customHeight="1">
       <c r="Q96" s="16" t="n"/>
@@ -3699,14 +4007,30 @@
           <t>Specific volume (L/kgda)</t>
         </is>
       </c>
-      <c r="S96" s="93" t="n"/>
-      <c r="T96" s="32" t="n"/>
-      <c r="U96" s="32" t="n"/>
-      <c r="V96" s="32" t="n"/>
-      <c r="W96" s="32" t="n"/>
-      <c r="X96" s="32" t="n"/>
-      <c r="Y96" s="32" t="n"/>
-      <c r="Z96" s="33" t="n"/>
+      <c r="S96" s="93" t="n">
+        <v>821.6458</v>
+      </c>
+      <c r="T96" s="32" t="n">
+        <v>838.7646</v>
+      </c>
+      <c r="U96" s="32" t="n">
+        <v>838.7646</v>
+      </c>
+      <c r="V96" s="32" t="n">
+        <v>831.8362</v>
+      </c>
+      <c r="W96" s="32" t="n">
+        <v>833.5029</v>
+      </c>
+      <c r="X96" s="32" t="n">
+        <v>846.5674</v>
+      </c>
+      <c r="Y96" s="32" t="n">
+        <v>846.5674</v>
+      </c>
+      <c r="Z96" s="33" t="n">
+        <v>847.4099</v>
+      </c>
     </row>
     <row r="97" ht="15" customHeight="1">
       <c r="Q97" s="16" t="n"/>
@@ -3715,14 +4039,30 @@
           <t>Enthalpy (J/gda)</t>
         </is>
       </c>
-      <c r="S97" s="93" t="n"/>
-      <c r="T97" s="32" t="n"/>
-      <c r="U97" s="32" t="n"/>
-      <c r="V97" s="32" t="n"/>
-      <c r="W97" s="32" t="n"/>
-      <c r="X97" s="32" t="n"/>
-      <c r="Y97" s="32" t="n"/>
-      <c r="Z97" s="33" t="n"/>
+      <c r="S97" s="93" t="n">
+        <v>23.1623</v>
+      </c>
+      <c r="T97" s="32" t="n">
+        <v>31.9453</v>
+      </c>
+      <c r="U97" s="32" t="n">
+        <v>31.9453</v>
+      </c>
+      <c r="V97" s="32" t="n">
+        <v>29.4824</v>
+      </c>
+      <c r="W97" s="32" t="n">
+        <v>30.0749</v>
+      </c>
+      <c r="X97" s="32" t="n">
+        <v>36.1641</v>
+      </c>
+      <c r="Y97" s="32" t="n">
+        <v>36.1641</v>
+      </c>
+      <c r="Z97" s="33" t="n">
+        <v>36.4636</v>
+      </c>
     </row>
     <row r="98" ht="15" customHeight="1">
       <c r="B98" s="4" t="n"/>
@@ -3732,18 +4072,32 @@
           <t>Mass flow rate (kgda/s)</t>
         </is>
       </c>
-      <c r="S98" s="94" t="n"/>
-      <c r="T98" s="39" t="n"/>
-      <c r="U98" s="39" t="n"/>
-      <c r="V98" s="39" t="n"/>
-      <c r="W98" s="39" t="n"/>
+      <c r="S98" s="94" t="n">
+        <v>0.112991</v>
+      </c>
+      <c r="T98" s="39" t="n">
+        <v>0.338544</v>
+      </c>
+      <c r="U98" s="39" t="n">
+        <v>0.338544</v>
+      </c>
+      <c r="V98" s="39" t="n">
+        <v>0.338544</v>
+      </c>
+      <c r="W98" s="39" t="n">
+        <v>0.338544</v>
+      </c>
       <c r="X98" s="39" t="inlineStr">
         <is>
           <t>n/a*</t>
         </is>
       </c>
-      <c r="Y98" s="39" t="n"/>
-      <c r="Z98" s="40" t="n"/>
+      <c r="Y98" s="39" t="n">
+        <v>0.225543</v>
+      </c>
+      <c r="Z98" s="40" t="n">
+        <v>0.225543</v>
+      </c>
     </row>
     <row r="99" ht="15" customHeight="1">
       <c r="B99" s="41" t="n"/>
@@ -3757,14 +4111,30 @@
           <t>Dry bulb temperature (°C)</t>
         </is>
       </c>
-      <c r="S99" s="92" t="n"/>
-      <c r="T99" s="28" t="n"/>
-      <c r="U99" s="28" t="n"/>
-      <c r="V99" s="28" t="n"/>
-      <c r="W99" s="28" t="n"/>
-      <c r="X99" s="28" t="n"/>
-      <c r="Y99" s="28" t="n"/>
-      <c r="Z99" s="29" t="n"/>
+      <c r="S99" s="92" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="T99" s="28" t="n">
+        <v>24.9979</v>
+      </c>
+      <c r="U99" s="28" t="n">
+        <v>24.9979</v>
+      </c>
+      <c r="V99" s="28" t="n">
+        <v>14.7711</v>
+      </c>
+      <c r="W99" s="28" t="n">
+        <v>15.3471</v>
+      </c>
+      <c r="X99" s="28" t="n">
+        <v>23.7524</v>
+      </c>
+      <c r="Y99" s="28" t="n">
+        <v>23.7524</v>
+      </c>
+      <c r="Z99" s="29" t="n">
+        <v>24.0474</v>
+      </c>
     </row>
     <row r="100" ht="15" customHeight="1">
       <c r="Q100" s="16" t="n"/>
@@ -3773,14 +4143,30 @@
           <t>Humidity ratio (g/gda)</t>
         </is>
       </c>
-      <c r="S100" s="93" t="n"/>
-      <c r="T100" s="32" t="n"/>
-      <c r="U100" s="32" t="n"/>
-      <c r="V100" s="32" t="n"/>
-      <c r="W100" s="32" t="n"/>
-      <c r="X100" s="32" t="n"/>
-      <c r="Y100" s="32" t="n"/>
-      <c r="Z100" s="33" t="n"/>
+      <c r="S100" s="93" t="n">
+        <v>0.01698</v>
+      </c>
+      <c r="T100" s="32" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="U100" s="32" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="V100" s="32" t="n">
+        <v>0.0105</v>
+      </c>
+      <c r="W100" s="32" t="n">
+        <v>0.0105</v>
+      </c>
+      <c r="X100" s="32" t="n">
+        <v>0.0112</v>
+      </c>
+      <c r="Y100" s="32" t="n">
+        <v>0.0112</v>
+      </c>
+      <c r="Z100" s="33" t="n">
+        <v>0.0112</v>
+      </c>
     </row>
     <row r="101" ht="15" customHeight="1">
       <c r="Q101" s="16" t="n"/>
@@ -3789,14 +4175,30 @@
           <t>Specific volume (L/kgda)</t>
         </is>
       </c>
-      <c r="S101" s="93" t="n"/>
-      <c r="T101" s="32" t="n"/>
-      <c r="U101" s="32" t="n"/>
-      <c r="V101" s="32" t="n"/>
-      <c r="W101" s="32" t="n"/>
-      <c r="X101" s="32" t="n"/>
-      <c r="Y101" s="32" t="n"/>
-      <c r="Z101" s="33" t="n"/>
+      <c r="S101" s="93" t="n">
+        <v>873.2133</v>
+      </c>
+      <c r="T101" s="32" t="n">
+        <v>862.2728</v>
+      </c>
+      <c r="U101" s="32" t="n">
+        <v>862.2728</v>
+      </c>
+      <c r="V101" s="32" t="n">
+        <v>829.4173</v>
+      </c>
+      <c r="W101" s="32" t="n">
+        <v>831.0766</v>
+      </c>
+      <c r="X101" s="32" t="n">
+        <v>856.2365</v>
+      </c>
+      <c r="Y101" s="32" t="n">
+        <v>856.2365</v>
+      </c>
+      <c r="Z101" s="33" t="n">
+        <v>857.0873</v>
+      </c>
     </row>
     <row r="102" ht="15" customHeight="1">
       <c r="Q102" s="16" t="n"/>
@@ -3805,14 +4207,30 @@
           <t>Enthalpy (J/gda)</t>
         </is>
       </c>
-      <c r="S102" s="93" t="n"/>
-      <c r="T102" s="32" t="n"/>
-      <c r="U102" s="32" t="n"/>
-      <c r="V102" s="32" t="n"/>
-      <c r="W102" s="32" t="n"/>
-      <c r="X102" s="32" t="n"/>
-      <c r="Y102" s="32" t="n"/>
-      <c r="Z102" s="33" t="n"/>
+      <c r="S102" s="93" t="n">
+        <v>70.378</v>
+      </c>
+      <c r="T102" s="32" t="n">
+        <v>58.2653</v>
+      </c>
+      <c r="U102" s="32" t="n">
+        <v>58.2653</v>
+      </c>
+      <c r="V102" s="32" t="n">
+        <v>41.4087</v>
+      </c>
+      <c r="W102" s="32" t="n">
+        <v>41.9994</v>
+      </c>
+      <c r="X102" s="32" t="n">
+        <v>52.4009</v>
+      </c>
+      <c r="Y102" s="32" t="n">
+        <v>52.4009</v>
+      </c>
+      <c r="Z102" s="33" t="n">
+        <v>52.7038</v>
+      </c>
     </row>
     <row r="103" ht="15" customHeight="1">
       <c r="Q103" s="27" t="n"/>
@@ -3821,18 +4239,32 @@
           <t>Mass flow rate (kgda/s)</t>
         </is>
       </c>
-      <c r="S103" s="94" t="n"/>
-      <c r="T103" s="39" t="n"/>
-      <c r="U103" s="39" t="n"/>
-      <c r="V103" s="39" t="n"/>
-      <c r="W103" s="39" t="n"/>
+      <c r="S103" s="94" t="n">
+        <v>0.111398</v>
+      </c>
+      <c r="T103" s="39" t="n">
+        <v>0.335637</v>
+      </c>
+      <c r="U103" s="39" t="n">
+        <v>0.335637</v>
+      </c>
+      <c r="V103" s="39" t="n">
+        <v>0.336467</v>
+      </c>
+      <c r="W103" s="39" t="n">
+        <v>0.336467</v>
+      </c>
       <c r="X103" s="39" t="inlineStr">
         <is>
           <t>n/a*</t>
         </is>
       </c>
-      <c r="Y103" s="39" t="n"/>
-      <c r="Z103" s="40" t="n"/>
+      <c r="Y103" s="39" t="n">
+        <v>0.224199</v>
+      </c>
+      <c r="Z103" s="40" t="n">
+        <v>0.224199</v>
+      </c>
     </row>
     <row r="104" ht="15" customHeight="1">
       <c r="Q104" s="89" t="inlineStr">
@@ -3845,14 +4277,30 @@
           <t>Dry bulb temperature (°C)</t>
         </is>
       </c>
-      <c r="S104" s="92" t="n"/>
-      <c r="T104" s="28" t="n"/>
-      <c r="U104" s="28" t="n"/>
-      <c r="V104" s="28" t="n"/>
-      <c r="W104" s="28" t="n"/>
-      <c r="X104" s="28" t="n"/>
-      <c r="Y104" s="28" t="n"/>
-      <c r="Z104" s="29" t="n"/>
+      <c r="S104" s="92" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="T104" s="28" t="n">
+        <v>24.0252</v>
+      </c>
+      <c r="U104" s="28" t="n">
+        <v>24.0252</v>
+      </c>
+      <c r="V104" s="28" t="n">
+        <v>18.4724</v>
+      </c>
+      <c r="W104" s="28" t="n">
+        <v>19.0565</v>
+      </c>
+      <c r="X104" s="28" t="n">
+        <v>23.2932</v>
+      </c>
+      <c r="Y104" s="28" t="n">
+        <v>23.2932</v>
+      </c>
+      <c r="Z104" s="29" t="n">
+        <v>23.5882</v>
+      </c>
     </row>
     <row r="105" ht="15" customHeight="1">
       <c r="Q105" s="16" t="n"/>
@@ -3861,14 +4309,30 @@
           <t>Humidity ratio (g/gda)</t>
         </is>
       </c>
-      <c r="S105" s="93" t="n"/>
-      <c r="T105" s="32" t="n"/>
-      <c r="U105" s="32" t="n"/>
-      <c r="V105" s="32" t="n"/>
-      <c r="W105" s="32" t="n"/>
-      <c r="X105" s="32" t="n"/>
-      <c r="Y105" s="32" t="n"/>
-      <c r="Z105" s="33" t="n"/>
+      <c r="S105" s="93" t="n">
+        <v>0.004579</v>
+      </c>
+      <c r="T105" s="32" t="n">
+        <v>0.0059</v>
+      </c>
+      <c r="U105" s="32" t="n">
+        <v>0.0059</v>
+      </c>
+      <c r="V105" s="32" t="n">
+        <v>0.0059</v>
+      </c>
+      <c r="W105" s="32" t="n">
+        <v>0.0059</v>
+      </c>
+      <c r="X105" s="32" t="n">
+        <v>0.0065</v>
+      </c>
+      <c r="Y105" s="32" t="n">
+        <v>0.0065</v>
+      </c>
+      <c r="Z105" s="33" t="n">
+        <v>0.0065</v>
+      </c>
     </row>
     <row r="106" ht="15" customHeight="1">
       <c r="Q106" s="16" t="n"/>
@@ -3877,14 +4341,30 @@
           <t>Specific volume (L/kgda)</t>
         </is>
       </c>
-      <c r="S106" s="93" t="n"/>
-      <c r="T106" s="32" t="n"/>
-      <c r="U106" s="32" t="n"/>
-      <c r="V106" s="32" t="n"/>
-      <c r="W106" s="32" t="n"/>
-      <c r="X106" s="32" t="n"/>
-      <c r="Y106" s="32" t="n"/>
-      <c r="Z106" s="33" t="n"/>
+      <c r="S106" s="93" t="n">
+        <v>850.5575</v>
+      </c>
+      <c r="T106" s="32" t="n">
+        <v>849.8492</v>
+      </c>
+      <c r="U106" s="32" t="n">
+        <v>849.8492</v>
+      </c>
+      <c r="V106" s="32" t="n">
+        <v>833.9695</v>
+      </c>
+      <c r="W106" s="32" t="n">
+        <v>835.6399</v>
+      </c>
+      <c r="X106" s="32" t="n">
+        <v>848.566</v>
+      </c>
+      <c r="Y106" s="32" t="n">
+        <v>848.566</v>
+      </c>
+      <c r="Z106" s="33" t="n">
+        <v>849.4104</v>
+      </c>
     </row>
     <row r="107" ht="15" customHeight="1">
       <c r="Q107" s="16" t="n"/>
@@ -3893,14 +4373,30 @@
           <t>Enthalpy (J/gda)</t>
         </is>
       </c>
-      <c r="S107" s="93" t="n"/>
-      <c r="T107" s="32" t="n"/>
-      <c r="U107" s="32" t="n"/>
-      <c r="V107" s="32" t="n"/>
-      <c r="W107" s="32" t="n"/>
-      <c r="X107" s="32" t="n"/>
-      <c r="Y107" s="32" t="n"/>
-      <c r="Z107" s="33" t="n"/>
+      <c r="S107" s="93" t="n">
+        <v>36.7136</v>
+      </c>
+      <c r="T107" s="32" t="n">
+        <v>39.1889</v>
+      </c>
+      <c r="U107" s="32" t="n">
+        <v>39.1889</v>
+      </c>
+      <c r="V107" s="32" t="n">
+        <v>33.5419</v>
+      </c>
+      <c r="W107" s="32" t="n">
+        <v>34.1359</v>
+      </c>
+      <c r="X107" s="32" t="n">
+        <v>39.9711</v>
+      </c>
+      <c r="Y107" s="32" t="n">
+        <v>39.9711</v>
+      </c>
+      <c r="Z107" s="33" t="n">
+        <v>40.2714</v>
+      </c>
     </row>
     <row r="108" ht="15" customHeight="1">
       <c r="Q108" s="27" t="n"/>
@@ -3909,18 +4405,32 @@
           <t>Mass flow rate (kgda/s)</t>
         </is>
       </c>
-      <c r="S108" s="94" t="n"/>
-      <c r="T108" s="39" t="n"/>
-      <c r="U108" s="39" t="n"/>
-      <c r="V108" s="39" t="n"/>
-      <c r="W108" s="39" t="n"/>
+      <c r="S108" s="94" t="n">
+        <v>0.112748</v>
+      </c>
+      <c r="T108" s="39" t="n">
+        <v>0.338006</v>
+      </c>
+      <c r="U108" s="39" t="n">
+        <v>0.338006</v>
+      </c>
+      <c r="V108" s="39" t="n">
+        <v>0.338006</v>
+      </c>
+      <c r="W108" s="39" t="n">
+        <v>0.338006</v>
+      </c>
       <c r="X108" s="39" t="inlineStr">
         <is>
           <t>n/a*</t>
         </is>
       </c>
-      <c r="Y108" s="39" t="n"/>
-      <c r="Z108" s="40" t="n"/>
+      <c r="Y108" s="39" t="n">
+        <v>0.225272</v>
+      </c>
+      <c r="Z108" s="40" t="n">
+        <v>0.225272</v>
+      </c>
     </row>
     <row r="109" ht="15" customHeight="1">
       <c r="Q109" s="89" t="inlineStr">
@@ -3933,14 +4443,30 @@
           <t>Dry bulb temperature (°C)</t>
         </is>
       </c>
-      <c r="S109" s="92" t="n"/>
-      <c r="T109" s="28" t="n"/>
-      <c r="U109" s="28" t="n"/>
-      <c r="V109" s="28" t="n"/>
-      <c r="W109" s="28" t="n"/>
-      <c r="X109" s="28" t="n"/>
-      <c r="Y109" s="28" t="n"/>
-      <c r="Z109" s="29" t="n"/>
+      <c r="S109" s="92" t="n">
+        <v>23</v>
+      </c>
+      <c r="T109" s="28" t="n">
+        <v>23.3621</v>
+      </c>
+      <c r="U109" s="28" t="n">
+        <v>23.3621</v>
+      </c>
+      <c r="V109" s="28" t="n">
+        <v>18.4857</v>
+      </c>
+      <c r="W109" s="28" t="n">
+        <v>19.0688</v>
+      </c>
+      <c r="X109" s="28" t="n">
+        <v>23.2484</v>
+      </c>
+      <c r="Y109" s="28" t="n">
+        <v>23.2484</v>
+      </c>
+      <c r="Z109" s="29" t="n">
+        <v>23.5434</v>
+      </c>
     </row>
     <row r="110" ht="15" customHeight="1">
       <c r="Q110" s="16" t="n"/>
@@ -3949,14 +4475,30 @@
           <t>Humidity ratio (g/gda)</t>
         </is>
       </c>
-      <c r="S110" s="93" t="n"/>
-      <c r="T110" s="32" t="n"/>
-      <c r="U110" s="32" t="n"/>
-      <c r="V110" s="32" t="n"/>
-      <c r="W110" s="32" t="n"/>
-      <c r="X110" s="32" t="n"/>
-      <c r="Y110" s="32" t="n"/>
-      <c r="Z110" s="33" t="n"/>
+      <c r="S110" s="93" t="n">
+        <v>0.015743</v>
+      </c>
+      <c r="T110" s="32" t="n">
+        <v>0.0145</v>
+      </c>
+      <c r="U110" s="32" t="n">
+        <v>0.0145</v>
+      </c>
+      <c r="V110" s="32" t="n">
+        <v>0.0133</v>
+      </c>
+      <c r="W110" s="32" t="n">
+        <v>0.0133</v>
+      </c>
+      <c r="X110" s="32" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="Y110" s="32" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="Z110" s="33" t="n">
+        <v>0.014</v>
+      </c>
     </row>
     <row r="111" ht="15" customHeight="1">
       <c r="Q111" s="16" t="n"/>
@@ -3965,14 +4507,30 @@
           <t>Specific volume (L/kgda)</t>
         </is>
       </c>
-      <c r="S111" s="93" t="n"/>
-      <c r="T111" s="32" t="n"/>
-      <c r="U111" s="32" t="n"/>
-      <c r="V111" s="32" t="n"/>
-      <c r="W111" s="32" t="n"/>
-      <c r="X111" s="32" t="n"/>
-      <c r="Y111" s="32" t="n"/>
-      <c r="Z111" s="33" t="n"/>
+      <c r="S111" s="93" t="n">
+        <v>860.1948</v>
+      </c>
+      <c r="T111" s="32" t="n">
+        <v>859.5678</v>
+      </c>
+      <c r="U111" s="32" t="n">
+        <v>859.5678</v>
+      </c>
+      <c r="V111" s="32" t="n">
+        <v>843.8374</v>
+      </c>
+      <c r="W111" s="32" t="n">
+        <v>845.5246</v>
+      </c>
+      <c r="X111" s="32" t="n">
+        <v>858.5632000000001</v>
+      </c>
+      <c r="Y111" s="32" t="n">
+        <v>858.5632000000001</v>
+      </c>
+      <c r="Z111" s="33" t="n">
+        <v>859.4177</v>
+      </c>
     </row>
     <row r="112" ht="15" customHeight="1">
       <c r="Q112" s="16" t="n"/>
@@ -3981,14 +4539,30 @@
           <t>Enthalpy (J/gda)</t>
         </is>
       </c>
-      <c r="S112" s="93" t="n"/>
-      <c r="T112" s="32" t="n"/>
-      <c r="U112" s="32" t="n"/>
-      <c r="V112" s="32" t="n"/>
-      <c r="W112" s="32" t="n"/>
-      <c r="X112" s="32" t="n"/>
-      <c r="Y112" s="32" t="n"/>
-      <c r="Z112" s="33" t="n"/>
+      <c r="S112" s="93" t="n">
+        <v>63.1847</v>
+      </c>
+      <c r="T112" s="32" t="n">
+        <v>60.3968</v>
+      </c>
+      <c r="U112" s="32" t="n">
+        <v>60.3968</v>
+      </c>
+      <c r="V112" s="32" t="n">
+        <v>52.3172</v>
+      </c>
+      <c r="W112" s="32" t="n">
+        <v>52.9182</v>
+      </c>
+      <c r="X112" s="32" t="n">
+        <v>59.0073</v>
+      </c>
+      <c r="Y112" s="32" t="n">
+        <v>59.0073</v>
+      </c>
+      <c r="Z112" s="33" t="n">
+        <v>59.3117</v>
+      </c>
     </row>
     <row r="113" ht="15" customHeight="1">
       <c r="Q113" s="27" t="n"/>
@@ -3997,18 +4571,32 @@
           <t>Mass flow rate (kgda/s)</t>
         </is>
       </c>
-      <c r="S113" s="94" t="n"/>
-      <c r="T113" s="39" t="n"/>
-      <c r="U113" s="39" t="n"/>
-      <c r="V113" s="39" t="n"/>
-      <c r="W113" s="39" t="n"/>
+      <c r="S113" s="94" t="n">
+        <v>0.111679</v>
+      </c>
+      <c r="T113" s="39" t="n">
+        <v>0.33514</v>
+      </c>
+      <c r="U113" s="39" t="n">
+        <v>0.33514</v>
+      </c>
+      <c r="V113" s="39" t="n">
+        <v>0.335537</v>
+      </c>
+      <c r="W113" s="39" t="n">
+        <v>0.335537</v>
+      </c>
       <c r="X113" s="39" t="inlineStr">
         <is>
           <t>n/a*</t>
         </is>
       </c>
-      <c r="Y113" s="39" t="n"/>
-      <c r="Z113" s="40" t="n"/>
+      <c r="Y113" s="39" t="n">
+        <v>0.223434</v>
+      </c>
+      <c r="Z113" s="40" t="n">
+        <v>0.223434</v>
+      </c>
     </row>
     <row r="114" ht="15" customHeight="1">
       <c r="Q114" s="89" t="inlineStr">
@@ -4021,14 +4609,30 @@
           <t>Dry bulb temperature (°C)</t>
         </is>
       </c>
-      <c r="S114" s="92" t="n"/>
-      <c r="T114" s="28" t="n"/>
-      <c r="U114" s="28" t="n"/>
-      <c r="V114" s="28" t="n"/>
-      <c r="W114" s="28" t="n"/>
-      <c r="X114" s="28" t="n"/>
-      <c r="Y114" s="28" t="n"/>
-      <c r="Z114" s="29" t="n"/>
+      <c r="S114" s="92" t="n">
+        <v>23</v>
+      </c>
+      <c r="T114" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="U114" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="V114" s="28" t="n">
+        <v>18.4857</v>
+      </c>
+      <c r="W114" s="28" t="n">
+        <v>19.0688</v>
+      </c>
+      <c r="X114" s="28" t="n">
+        <v>23.2484</v>
+      </c>
+      <c r="Y114" s="28" t="n">
+        <v>23.2484</v>
+      </c>
+      <c r="Z114" s="29" t="n">
+        <v>23.5434</v>
+      </c>
     </row>
     <row r="115" ht="15" customHeight="1">
       <c r="Q115" s="16" t="n"/>
@@ -4037,14 +4641,30 @@
           <t>Humidity ratio (g/gda)</t>
         </is>
       </c>
-      <c r="S115" s="93" t="n"/>
-      <c r="T115" s="32" t="n"/>
-      <c r="U115" s="32" t="n"/>
-      <c r="V115" s="32" t="n"/>
-      <c r="W115" s="32" t="n"/>
-      <c r="X115" s="32" t="n"/>
-      <c r="Y115" s="32" t="n"/>
-      <c r="Z115" s="33" t="n"/>
+      <c r="S115" s="93" t="n">
+        <v>0.015743</v>
+      </c>
+      <c r="T115" s="32" t="n">
+        <v>0.0156</v>
+      </c>
+      <c r="U115" s="32" t="n">
+        <v>0.0156</v>
+      </c>
+      <c r="V115" s="32" t="n">
+        <v>0.0133</v>
+      </c>
+      <c r="W115" s="32" t="n">
+        <v>0.0133</v>
+      </c>
+      <c r="X115" s="32" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="Y115" s="32" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="Z115" s="33" t="n">
+        <v>0.014</v>
+      </c>
     </row>
     <row r="116" ht="15" customHeight="1">
       <c r="Q116" s="16" t="n"/>
@@ -4053,14 +4673,30 @@
           <t>Specific volume (L/kgda)</t>
         </is>
       </c>
-      <c r="S116" s="93" t="n"/>
-      <c r="T116" s="32" t="n"/>
-      <c r="U116" s="32" t="n"/>
-      <c r="V116" s="32" t="n"/>
-      <c r="W116" s="32" t="n"/>
-      <c r="X116" s="32" t="n"/>
-      <c r="Y116" s="32" t="n"/>
-      <c r="Z116" s="33" t="n"/>
+      <c r="S116" s="93" t="n">
+        <v>860.1948</v>
+      </c>
+      <c r="T116" s="32" t="n">
+        <v>860.0019</v>
+      </c>
+      <c r="U116" s="32" t="n">
+        <v>860.0019</v>
+      </c>
+      <c r="V116" s="32" t="n">
+        <v>843.8374</v>
+      </c>
+      <c r="W116" s="32" t="n">
+        <v>845.5246</v>
+      </c>
+      <c r="X116" s="32" t="n">
+        <v>858.5632000000001</v>
+      </c>
+      <c r="Y116" s="32" t="n">
+        <v>858.5632000000001</v>
+      </c>
+      <c r="Z116" s="33" t="n">
+        <v>859.4177</v>
+      </c>
     </row>
     <row r="117" ht="15" customHeight="1">
       <c r="Q117" s="16" t="n"/>
@@ -4069,14 +4705,30 @@
           <t>Enthalpy (J/gda)</t>
         </is>
       </c>
-      <c r="S117" s="93" t="n"/>
-      <c r="T117" s="32" t="n"/>
-      <c r="U117" s="32" t="n"/>
-      <c r="V117" s="32" t="n"/>
-      <c r="W117" s="32" t="n"/>
-      <c r="X117" s="32" t="n"/>
-      <c r="Y117" s="32" t="n"/>
-      <c r="Z117" s="33" t="n"/>
+      <c r="S117" s="93" t="n">
+        <v>63.1847</v>
+      </c>
+      <c r="T117" s="32" t="n">
+        <v>62.821</v>
+      </c>
+      <c r="U117" s="32" t="n">
+        <v>62.821</v>
+      </c>
+      <c r="V117" s="32" t="n">
+        <v>52.3172</v>
+      </c>
+      <c r="W117" s="32" t="n">
+        <v>52.9182</v>
+      </c>
+      <c r="X117" s="32" t="n">
+        <v>59.0073</v>
+      </c>
+      <c r="Y117" s="32" t="n">
+        <v>59.0073</v>
+      </c>
+      <c r="Z117" s="33" t="n">
+        <v>59.3117</v>
+      </c>
     </row>
     <row r="118" ht="15" customHeight="1">
       <c r="Q118" s="27" t="n"/>
@@ -4085,18 +4737,32 @@
           <t>Mass flow rate (kgda/s)</t>
         </is>
       </c>
-      <c r="S118" s="94" t="n"/>
-      <c r="T118" s="39" t="n"/>
-      <c r="U118" s="39" t="n"/>
-      <c r="V118" s="39" t="n"/>
-      <c r="W118" s="39" t="n"/>
+      <c r="S118" s="94" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="T118" s="39" t="n">
+        <v>0.334777</v>
+      </c>
+      <c r="U118" s="39" t="n">
+        <v>0.334777</v>
+      </c>
+      <c r="V118" s="39" t="n">
+        <v>0.335537</v>
+      </c>
+      <c r="W118" s="39" t="n">
+        <v>0.335537</v>
+      </c>
       <c r="X118" s="39" t="inlineStr">
         <is>
           <t>n/a*</t>
         </is>
       </c>
-      <c r="Y118" s="39" t="n"/>
-      <c r="Z118" s="40" t="n"/>
+      <c r="Y118" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z118" s="40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="119" ht="15" customHeight="1">
       <c r="Q119" s="89" t="inlineStr">
@@ -4109,14 +4775,30 @@
           <t>Dry bulb temperature (°C)</t>
         </is>
       </c>
-      <c r="S119" s="92" t="n"/>
-      <c r="T119" s="28" t="n"/>
-      <c r="U119" s="28" t="n"/>
-      <c r="V119" s="28" t="n"/>
-      <c r="W119" s="28" t="n"/>
-      <c r="X119" s="28" t="n"/>
-      <c r="Y119" s="28" t="n"/>
-      <c r="Z119" s="29" t="n"/>
+      <c r="S119" s="92" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="T119" s="28" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="U119" s="28" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="V119" s="28" t="n">
+        <v>18.4699</v>
+      </c>
+      <c r="W119" s="28" t="n">
+        <v>19.0542</v>
+      </c>
+      <c r="X119" s="28" t="n">
+        <v>23.3016</v>
+      </c>
+      <c r="Y119" s="28" t="n">
+        <v>23.3016</v>
+      </c>
+      <c r="Z119" s="29" t="n">
+        <v>23.5966</v>
+      </c>
     </row>
     <row r="120" ht="15" customHeight="1">
       <c r="Q120" s="16" t="n"/>
@@ -4125,14 +4807,30 @@
           <t>Humidity ratio (g/gda)</t>
         </is>
       </c>
-      <c r="S120" s="93" t="n"/>
-      <c r="T120" s="32" t="n"/>
-      <c r="U120" s="32" t="n"/>
-      <c r="V120" s="32" t="n"/>
-      <c r="W120" s="32" t="n"/>
-      <c r="X120" s="32" t="n"/>
-      <c r="Y120" s="32" t="n"/>
-      <c r="Z120" s="33" t="n"/>
+      <c r="S120" s="93" t="n">
+        <v>0.004579</v>
+      </c>
+      <c r="T120" s="32" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="U120" s="32" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="V120" s="32" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="W120" s="32" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="X120" s="32" t="n">
+        <v>0.0052</v>
+      </c>
+      <c r="Y120" s="32" t="n">
+        <v>0.0052</v>
+      </c>
+      <c r="Z120" s="33" t="n">
+        <v>0.0052</v>
+      </c>
     </row>
     <row r="121" ht="15" customHeight="1">
       <c r="Q121" s="16" t="n"/>
@@ -4141,14 +4839,30 @@
           <t>Specific volume (L/kgda)</t>
         </is>
       </c>
-      <c r="S121" s="93" t="n"/>
-      <c r="T121" s="32" t="n"/>
-      <c r="U121" s="32" t="n"/>
-      <c r="V121" s="32" t="n"/>
-      <c r="W121" s="32" t="n"/>
-      <c r="X121" s="32" t="n"/>
-      <c r="Y121" s="32" t="n"/>
-      <c r="Z121" s="33" t="n"/>
+      <c r="S121" s="93" t="n">
+        <v>850.5575</v>
+      </c>
+      <c r="T121" s="32" t="n">
+        <v>850.4503</v>
+      </c>
+      <c r="U121" s="32" t="n">
+        <v>850.4503</v>
+      </c>
+      <c r="V121" s="32" t="n">
+        <v>832.1027</v>
+      </c>
+      <c r="W121" s="32" t="n">
+        <v>833.77</v>
+      </c>
+      <c r="X121" s="32" t="n">
+        <v>846.8346</v>
+      </c>
+      <c r="Y121" s="32" t="n">
+        <v>846.8346</v>
+      </c>
+      <c r="Z121" s="33" t="n">
+        <v>847.6772999999999</v>
+      </c>
     </row>
     <row r="122" ht="15" customHeight="1">
       <c r="Q122" s="16" t="n"/>
@@ -4157,14 +4871,30 @@
           <t>Enthalpy (J/gda)</t>
         </is>
       </c>
-      <c r="S122" s="93" t="n"/>
-      <c r="T122" s="32" t="n"/>
-      <c r="U122" s="32" t="n"/>
-      <c r="V122" s="32" t="n"/>
-      <c r="W122" s="32" t="n"/>
-      <c r="X122" s="32" t="n"/>
-      <c r="Y122" s="32" t="n"/>
-      <c r="Z122" s="33" t="n"/>
+      <c r="S122" s="93" t="n">
+        <v>36.7136</v>
+      </c>
+      <c r="T122" s="32" t="n">
+        <v>36.5123</v>
+      </c>
+      <c r="U122" s="32" t="n">
+        <v>36.5123</v>
+      </c>
+      <c r="V122" s="32" t="n">
+        <v>29.9898</v>
+      </c>
+      <c r="W122" s="32" t="n">
+        <v>30.5825</v>
+      </c>
+      <c r="X122" s="32" t="n">
+        <v>36.672</v>
+      </c>
+      <c r="Y122" s="32" t="n">
+        <v>36.672</v>
+      </c>
+      <c r="Z122" s="33" t="n">
+        <v>36.9716</v>
+      </c>
     </row>
     <row r="123" ht="15" customHeight="1">
       <c r="Q123" s="27" t="n"/>
@@ -4173,18 +4903,32 @@
           <t>Mass flow rate (kgda/s)</t>
         </is>
       </c>
-      <c r="S123" s="94" t="n"/>
-      <c r="T123" s="39" t="n"/>
-      <c r="U123" s="39" t="n"/>
-      <c r="V123" s="39" t="n"/>
-      <c r="W123" s="39" t="n"/>
+      <c r="S123" s="94" t="n">
+        <v>0.33845</v>
+      </c>
+      <c r="T123" s="39" t="n">
+        <v>0.338477</v>
+      </c>
+      <c r="U123" s="39" t="n">
+        <v>0.338477</v>
+      </c>
+      <c r="V123" s="39" t="n">
+        <v>0.338477</v>
+      </c>
+      <c r="W123" s="39" t="n">
+        <v>0.338477</v>
+      </c>
       <c r="X123" s="39" t="inlineStr">
         <is>
           <t>n/a*</t>
         </is>
       </c>
-      <c r="Y123" s="39" t="n"/>
-      <c r="Z123" s="40" t="n"/>
+      <c r="Y123" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z123" s="40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="124" ht="7.5" customHeight="1"/>
     <row r="125" ht="15" customHeight="1">
@@ -4797,17 +5541,39 @@
           <t>Dry bulb temperature (°C)</t>
         </is>
       </c>
-      <c r="S137" s="92" t="n"/>
-      <c r="T137" s="28" t="n"/>
-      <c r="U137" s="28" t="n"/>
-      <c r="V137" s="28" t="n"/>
-      <c r="W137" s="28" t="n"/>
-      <c r="X137" s="28" t="n"/>
-      <c r="Y137" s="28" t="n"/>
-      <c r="Z137" s="28" t="n"/>
-      <c r="AA137" s="28" t="n"/>
-      <c r="AB137" s="28" t="n"/>
-      <c r="AC137" s="29" t="n"/>
+      <c r="S137" s="92" t="n">
+        <v>-29</v>
+      </c>
+      <c r="T137" s="28" t="n">
+        <v>2.1554</v>
+      </c>
+      <c r="U137" s="28" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="V137" s="28" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="W137" s="28" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="X137" s="28" t="n">
+        <v>29.5472</v>
+      </c>
+      <c r="Y137" s="28" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z137" s="28" t="n">
+        <v>21.1029</v>
+      </c>
+      <c r="AA137" s="28" t="n">
+        <v>22.2112</v>
+      </c>
+      <c r="AB137" s="28" t="n">
+        <v>21.6996</v>
+      </c>
+      <c r="AC137" s="29" t="n">
+        <v>21.9946</v>
+      </c>
     </row>
     <row r="138" ht="15" customHeight="1">
       <c r="B138" s="34" t="inlineStr">
@@ -4860,17 +5626,39 @@
           <t>Humidity ratio (g/gda)</t>
         </is>
       </c>
-      <c r="S138" s="93" t="n"/>
-      <c r="T138" s="32" t="n"/>
-      <c r="U138" s="32" t="n"/>
-      <c r="V138" s="32" t="n"/>
-      <c r="W138" s="32" t="n"/>
-      <c r="X138" s="32" t="n"/>
-      <c r="Y138" s="32" t="n"/>
-      <c r="Z138" s="32" t="n"/>
-      <c r="AA138" s="32" t="n"/>
-      <c r="AB138" s="32" t="n"/>
-      <c r="AC138" s="33" t="n"/>
+      <c r="S138" s="93" t="n">
+        <v>0.000259</v>
+      </c>
+      <c r="T138" s="32" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="U138" s="32" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="V138" s="32" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="W138" s="32" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="X138" s="32" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="Y138" s="32" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="Z138" s="32" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="AA138" s="32" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="AB138" s="32" t="n">
+        <v>0.002308</v>
+      </c>
+      <c r="AC138" s="33" t="n">
+        <v>0.002308</v>
+      </c>
     </row>
     <row r="139" ht="15" customHeight="1">
       <c r="B139" s="34" t="inlineStr">
@@ -4923,17 +5711,39 @@
           <t>Specific volume (L/kgda)</t>
         </is>
       </c>
-      <c r="S139" s="93" t="n"/>
-      <c r="T139" s="32" t="n"/>
-      <c r="U139" s="32" t="n"/>
-      <c r="V139" s="32" t="n"/>
-      <c r="W139" s="32" t="n"/>
-      <c r="X139" s="32" t="n"/>
-      <c r="Y139" s="32" t="n"/>
-      <c r="Z139" s="32" t="n"/>
-      <c r="AA139" s="32" t="n"/>
-      <c r="AB139" s="32" t="n"/>
-      <c r="AC139" s="33" t="n"/>
+      <c r="S139" s="93" t="n">
+        <v>691.9367</v>
+      </c>
+      <c r="T139" s="32" t="n">
+        <v>781.7893</v>
+      </c>
+      <c r="U139" s="32" t="n">
+        <v>796.1713</v>
+      </c>
+      <c r="V139" s="32" t="n">
+        <v>796.1713</v>
+      </c>
+      <c r="W139" s="32" t="n">
+        <v>797.6763999999999</v>
+      </c>
+      <c r="X139" s="32" t="n">
+        <v>859.5743</v>
+      </c>
+      <c r="Y139" s="32" t="n">
+        <v>855.1807</v>
+      </c>
+      <c r="Z139" s="32" t="n">
+        <v>836.533</v>
+      </c>
+      <c r="AA139" s="32" t="n">
+        <v>839.9529</v>
+      </c>
+      <c r="AB139" s="32" t="n">
+        <v>838.3741</v>
+      </c>
+      <c r="AC139" s="33" t="n">
+        <v>839.213</v>
+      </c>
     </row>
     <row r="140" ht="15" customHeight="1">
       <c r="B140" s="34" t="inlineStr">
@@ -4986,17 +5796,39 @@
           <t>Enthalpy (J/gda)</t>
         </is>
       </c>
-      <c r="S140" s="93" t="n"/>
-      <c r="T140" s="32" t="n"/>
-      <c r="U140" s="32" t="n"/>
-      <c r="V140" s="32" t="n"/>
-      <c r="W140" s="32" t="n"/>
-      <c r="X140" s="32" t="n"/>
-      <c r="Y140" s="32" t="n"/>
-      <c r="Z140" s="32" t="n"/>
-      <c r="AA140" s="32" t="n"/>
-      <c r="AB140" s="32" t="n"/>
-      <c r="AC140" s="33" t="n"/>
+      <c r="S140" s="93" t="n">
+        <v>-28.5402</v>
+      </c>
+      <c r="T140" s="32" t="n">
+        <v>5.9258</v>
+      </c>
+      <c r="U140" s="32" t="n">
+        <v>11.035</v>
+      </c>
+      <c r="V140" s="32" t="n">
+        <v>11.035</v>
+      </c>
+      <c r="W140" s="32" t="n">
+        <v>11.5696</v>
+      </c>
+      <c r="X140" s="32" t="n">
+        <v>33.5584</v>
+      </c>
+      <c r="Y140" s="32" t="n">
+        <v>31.9976</v>
+      </c>
+      <c r="Z140" s="32" t="n">
+        <v>26.8181</v>
+      </c>
+      <c r="AA140" s="32" t="n">
+        <v>28.446</v>
+      </c>
+      <c r="AB140" s="32" t="n">
+        <v>27.6945</v>
+      </c>
+      <c r="AC140" s="33" t="n">
+        <v>27.9925</v>
+      </c>
     </row>
     <row r="141" ht="15" customHeight="1">
       <c r="B141" s="34" t="inlineStr">
@@ -5049,13 +5881,27 @@
           <t>Mass flow rate (kgda/s)</t>
         </is>
       </c>
-      <c r="S141" s="94" t="n"/>
-      <c r="T141" s="39" t="n"/>
-      <c r="U141" s="39" t="n"/>
-      <c r="V141" s="39" t="n"/>
-      <c r="W141" s="39" t="n"/>
-      <c r="X141" s="39" t="n"/>
-      <c r="Y141" s="39" t="n"/>
+      <c r="S141" s="94" t="n">
+        <v>0.28992</v>
+      </c>
+      <c r="T141" s="39" t="n">
+        <v>0.7442839999999999</v>
+      </c>
+      <c r="U141" s="39" t="n">
+        <v>0.7442839999999999</v>
+      </c>
+      <c r="V141" s="39" t="n">
+        <v>0.7442839999999999</v>
+      </c>
+      <c r="W141" s="39" t="n">
+        <v>0.7442839999999999</v>
+      </c>
+      <c r="X141" s="39" t="n">
+        <v>0.343585</v>
+      </c>
+      <c r="Y141" s="39" t="n">
+        <v>0.400799</v>
+      </c>
       <c r="Z141" s="39" t="inlineStr">
         <is>
           <t>n/a*</t>
@@ -5066,8 +5912,12 @@
           <t>n/a*</t>
         </is>
       </c>
-      <c r="AB141" s="39" t="n"/>
-      <c r="AC141" s="40" t="n"/>
+      <c r="AB141" s="39" t="n">
+        <v>0.454357</v>
+      </c>
+      <c r="AC141" s="40" t="n">
+        <v>0.454357</v>
+      </c>
     </row>
     <row r="142" ht="15" customHeight="1">
       <c r="B142" s="34" t="inlineStr">
@@ -5124,17 +5974,39 @@
           <t>Dry bulb temperature (°C)</t>
         </is>
       </c>
-      <c r="S142" s="92" t="n"/>
-      <c r="T142" s="28" t="n"/>
-      <c r="U142" s="28" t="n"/>
-      <c r="V142" s="28" t="n"/>
-      <c r="W142" s="28" t="n"/>
-      <c r="X142" s="28" t="n"/>
-      <c r="Y142" s="28" t="n"/>
-      <c r="Z142" s="28" t="n"/>
-      <c r="AA142" s="28" t="n"/>
-      <c r="AB142" s="28" t="n"/>
-      <c r="AC142" s="29" t="n"/>
+      <c r="S142" s="92" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="T142" s="28" t="n">
+        <v>20.7926</v>
+      </c>
+      <c r="U142" s="28" t="n">
+        <v>20.7926</v>
+      </c>
+      <c r="V142" s="28" t="n">
+        <v>12.1907</v>
+      </c>
+      <c r="W142" s="28" t="n">
+        <v>12.7508</v>
+      </c>
+      <c r="X142" s="28" t="n">
+        <v>19.0758</v>
+      </c>
+      <c r="Y142" s="28" t="n">
+        <v>18.6155</v>
+      </c>
+      <c r="Z142" s="28" t="n">
+        <v>23.2758</v>
+      </c>
+      <c r="AA142" s="28" t="n">
+        <v>24.3759</v>
+      </c>
+      <c r="AB142" s="28" t="n">
+        <v>23.8681</v>
+      </c>
+      <c r="AC142" s="29" t="n">
+        <v>24.1631</v>
+      </c>
     </row>
     <row r="143" ht="15" customHeight="1">
       <c r="B143" s="36" t="inlineStr">
@@ -5187,17 +6059,39 @@
           <t>Humidity ratio (g/gda)</t>
         </is>
       </c>
-      <c r="S143" s="93" t="n"/>
-      <c r="T143" s="32" t="n"/>
-      <c r="U143" s="32" t="n"/>
-      <c r="V143" s="32" t="n"/>
-      <c r="W143" s="32" t="n"/>
-      <c r="X143" s="32" t="n"/>
-      <c r="Y143" s="32" t="n"/>
-      <c r="Z143" s="32" t="n"/>
-      <c r="AA143" s="32" t="n"/>
-      <c r="AB143" s="32" t="n"/>
-      <c r="AC143" s="33" t="n"/>
+      <c r="S143" s="93" t="n">
+        <v>0.002992</v>
+      </c>
+      <c r="T143" s="32" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="U143" s="32" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="V143" s="32" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="W143" s="32" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="X143" s="32" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="Y143" s="32" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="Z143" s="32" t="n">
+        <v>0.0048</v>
+      </c>
+      <c r="AA143" s="32" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="AB143" s="32" t="n">
+        <v>0.004908</v>
+      </c>
+      <c r="AC143" s="33" t="n">
+        <v>0.004908</v>
+      </c>
     </row>
     <row r="144" ht="15" customHeight="1">
       <c r="Q144" s="16" t="n"/>
@@ -5206,17 +6100,39 @@
           <t>Specific volume (L/kgda)</t>
         </is>
       </c>
-      <c r="S144" s="93" t="n"/>
-      <c r="T144" s="32" t="n"/>
-      <c r="U144" s="32" t="n"/>
-      <c r="V144" s="32" t="n"/>
-      <c r="W144" s="32" t="n"/>
-      <c r="X144" s="32" t="n"/>
-      <c r="Y144" s="32" t="n"/>
-      <c r="Z144" s="32" t="n"/>
-      <c r="AA144" s="32" t="n"/>
-      <c r="AB144" s="32" t="n"/>
-      <c r="AC144" s="33" t="n"/>
+      <c r="S144" s="93" t="n">
+        <v>821.6458</v>
+      </c>
+      <c r="T144" s="32" t="n">
+        <v>838.3286000000001</v>
+      </c>
+      <c r="U144" s="32" t="n">
+        <v>838.3286000000001</v>
+      </c>
+      <c r="V144" s="32" t="n">
+        <v>813.7959</v>
+      </c>
+      <c r="W144" s="32" t="n">
+        <v>815.3933</v>
+      </c>
+      <c r="X144" s="32" t="n">
+        <v>833.4323000000001</v>
+      </c>
+      <c r="Y144" s="32" t="n">
+        <v>832.1195</v>
+      </c>
+      <c r="Z144" s="32" t="n">
+        <v>846.2209</v>
+      </c>
+      <c r="AA144" s="32" t="n">
+        <v>849.6324</v>
+      </c>
+      <c r="AB144" s="32" t="n">
+        <v>848.0575</v>
+      </c>
+      <c r="AC144" s="33" t="n">
+        <v>848.8998</v>
+      </c>
     </row>
     <row r="145" ht="15" customHeight="1">
       <c r="Q145" s="16" t="n"/>
@@ -5225,17 +6141,39 @@
           <t>Enthalpy (J/gda)</t>
         </is>
       </c>
-      <c r="S145" s="93" t="n"/>
-      <c r="T145" s="32" t="n"/>
-      <c r="U145" s="32" t="n"/>
-      <c r="V145" s="32" t="n"/>
-      <c r="W145" s="32" t="n"/>
-      <c r="X145" s="32" t="n"/>
-      <c r="Y145" s="32" t="n"/>
-      <c r="Z145" s="32" t="n"/>
-      <c r="AA145" s="32" t="n"/>
-      <c r="AB145" s="32" t="n"/>
-      <c r="AC145" s="33" t="n"/>
+      <c r="S145" s="93" t="n">
+        <v>23.1623</v>
+      </c>
+      <c r="T145" s="32" t="n">
+        <v>31.584</v>
+      </c>
+      <c r="U145" s="32" t="n">
+        <v>31.584</v>
+      </c>
+      <c r="V145" s="32" t="n">
+        <v>22.8633</v>
+      </c>
+      <c r="W145" s="32" t="n">
+        <v>23.4311</v>
+      </c>
+      <c r="X145" s="32" t="n">
+        <v>29.8435</v>
+      </c>
+      <c r="Y145" s="32" t="n">
+        <v>29.3768</v>
+      </c>
+      <c r="Z145" s="32" t="n">
+        <v>35.6281</v>
+      </c>
+      <c r="AA145" s="32" t="n">
+        <v>37.2539</v>
+      </c>
+      <c r="AB145" s="32" t="n">
+        <v>36.5033</v>
+      </c>
+      <c r="AC145" s="33" t="n">
+        <v>36.8028</v>
+      </c>
     </row>
     <row r="146" ht="15" customHeight="1">
       <c r="B146" s="4" t="n"/>
@@ -5245,13 +6183,27 @@
           <t>Mass flow rate (kgda/s)</t>
         </is>
       </c>
-      <c r="S146" s="94" t="n"/>
-      <c r="T146" s="39" t="n"/>
-      <c r="U146" s="39" t="n"/>
-      <c r="V146" s="39" t="n"/>
-      <c r="W146" s="39" t="n"/>
-      <c r="X146" s="39" t="n"/>
-      <c r="Y146" s="39" t="n"/>
+      <c r="S146" s="94" t="n">
+        <v>0.289145</v>
+      </c>
+      <c r="T146" s="39" t="n">
+        <v>0.742282</v>
+      </c>
+      <c r="U146" s="39" t="n">
+        <v>0.742282</v>
+      </c>
+      <c r="V146" s="39" t="n">
+        <v>0.742282</v>
+      </c>
+      <c r="W146" s="39" t="n">
+        <v>0.742282</v>
+      </c>
+      <c r="X146" s="39" t="n">
+        <v>0.342661</v>
+      </c>
+      <c r="Y146" s="39" t="n">
+        <v>0.399721</v>
+      </c>
       <c r="Z146" s="39" t="inlineStr">
         <is>
           <t>n/a*</t>
@@ -5262,8 +6214,12 @@
           <t>n/a*</t>
         </is>
       </c>
-      <c r="AB146" s="39" t="n"/>
-      <c r="AC146" s="40" t="n"/>
+      <c r="AB146" s="39" t="n">
+        <v>0.453166</v>
+      </c>
+      <c r="AC146" s="40" t="n">
+        <v>0.453166</v>
+      </c>
     </row>
     <row r="147" ht="15" customHeight="1">
       <c r="B147" s="41" t="n"/>
@@ -5277,17 +6233,39 @@
           <t>Dry bulb temperature (°C)</t>
         </is>
       </c>
-      <c r="S147" s="92" t="n"/>
-      <c r="T147" s="28" t="n"/>
-      <c r="U147" s="28" t="n"/>
-      <c r="V147" s="28" t="n"/>
-      <c r="W147" s="28" t="n"/>
-      <c r="X147" s="28" t="n"/>
-      <c r="Y147" s="28" t="n"/>
-      <c r="Z147" s="28" t="n"/>
-      <c r="AA147" s="28" t="n"/>
-      <c r="AB147" s="28" t="n"/>
-      <c r="AC147" s="29" t="n"/>
+      <c r="S147" s="92" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="T147" s="28" t="n">
+        <v>25.5153</v>
+      </c>
+      <c r="U147" s="28" t="n">
+        <v>25.5153</v>
+      </c>
+      <c r="V147" s="28" t="n">
+        <v>12.1907</v>
+      </c>
+      <c r="W147" s="28" t="n">
+        <v>12.7577</v>
+      </c>
+      <c r="X147" s="28" t="n">
+        <v>15.4205</v>
+      </c>
+      <c r="Y147" s="28" t="n">
+        <v>16.2763</v>
+      </c>
+      <c r="Z147" s="28" t="n">
+        <v>23.7518</v>
+      </c>
+      <c r="AA147" s="28" t="n">
+        <v>24.8422</v>
+      </c>
+      <c r="AB147" s="28" t="n">
+        <v>24.3389</v>
+      </c>
+      <c r="AC147" s="29" t="n">
+        <v>24.6339</v>
+      </c>
     </row>
     <row r="148" ht="15" customHeight="1">
       <c r="Q148" s="16" t="n"/>
@@ -5296,17 +6274,39 @@
           <t>Humidity ratio (g/gda)</t>
         </is>
       </c>
-      <c r="S148" s="93" t="n"/>
-      <c r="T148" s="32" t="n"/>
-      <c r="U148" s="32" t="n"/>
-      <c r="V148" s="32" t="n"/>
-      <c r="W148" s="32" t="n"/>
-      <c r="X148" s="32" t="n"/>
-      <c r="Y148" s="32" t="n"/>
-      <c r="Z148" s="32" t="n"/>
-      <c r="AA148" s="32" t="n"/>
-      <c r="AB148" s="32" t="n"/>
-      <c r="AC148" s="33" t="n"/>
+      <c r="S148" s="93" t="n">
+        <v>0.01698</v>
+      </c>
+      <c r="T148" s="32" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="U148" s="32" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="V148" s="32" t="n">
+        <v>0.008800000000000001</v>
+      </c>
+      <c r="W148" s="32" t="n">
+        <v>0.008800000000000001</v>
+      </c>
+      <c r="X148" s="32" t="n">
+        <v>0.008800000000000001</v>
+      </c>
+      <c r="Y148" s="32" t="n">
+        <v>0.008800000000000001</v>
+      </c>
+      <c r="Z148" s="32" t="n">
+        <v>0.0095</v>
+      </c>
+      <c r="AA148" s="32" t="n">
+        <v>0.0097</v>
+      </c>
+      <c r="AB148" s="32" t="n">
+        <v>0.009608</v>
+      </c>
+      <c r="AC148" s="33" t="n">
+        <v>0.009608</v>
+      </c>
     </row>
     <row r="149" ht="15" customHeight="1">
       <c r="Q149" s="16" t="n"/>
@@ -5315,17 +6315,39 @@
           <t>Specific volume (L/kgda)</t>
         </is>
       </c>
-      <c r="S149" s="93" t="n"/>
-      <c r="T149" s="32" t="n"/>
-      <c r="U149" s="32" t="n"/>
-      <c r="V149" s="32" t="n"/>
-      <c r="W149" s="32" t="n"/>
-      <c r="X149" s="32" t="n"/>
-      <c r="Y149" s="32" t="n"/>
-      <c r="Z149" s="32" t="n"/>
-      <c r="AA149" s="32" t="n"/>
-      <c r="AB149" s="32" t="n"/>
-      <c r="AC149" s="33" t="n"/>
+      <c r="S149" s="93" t="n">
+        <v>873.2133</v>
+      </c>
+      <c r="T149" s="32" t="n">
+        <v>862.953</v>
+      </c>
+      <c r="U149" s="32" t="n">
+        <v>862.953</v>
+      </c>
+      <c r="V149" s="32" t="n">
+        <v>819.7745</v>
+      </c>
+      <c r="W149" s="32" t="n">
+        <v>821.4034</v>
+      </c>
+      <c r="X149" s="32" t="n">
+        <v>829.0536</v>
+      </c>
+      <c r="Y149" s="32" t="n">
+        <v>831.5123</v>
+      </c>
+      <c r="Z149" s="32" t="n">
+        <v>853.9358</v>
+      </c>
+      <c r="AA149" s="32" t="n">
+        <v>857.3434</v>
+      </c>
+      <c r="AB149" s="32" t="n">
+        <v>855.7703</v>
+      </c>
+      <c r="AC149" s="33" t="n">
+        <v>856.6189000000001</v>
+      </c>
     </row>
     <row r="150" ht="15" customHeight="1">
       <c r="Q150" s="16" t="n"/>
@@ -5334,17 +6356,39 @@
           <t>Enthalpy (J/gda)</t>
         </is>
       </c>
-      <c r="S150" s="93" t="n"/>
-      <c r="T150" s="32" t="n"/>
-      <c r="U150" s="32" t="n"/>
-      <c r="V150" s="32" t="n"/>
-      <c r="W150" s="32" t="n"/>
-      <c r="X150" s="32" t="n"/>
-      <c r="Y150" s="32" t="n"/>
-      <c r="Z150" s="32" t="n"/>
-      <c r="AA150" s="32" t="n"/>
-      <c r="AB150" s="32" t="n"/>
-      <c r="AC150" s="33" t="n"/>
+      <c r="S150" s="93" t="n">
+        <v>70.378</v>
+      </c>
+      <c r="T150" s="32" t="n">
+        <v>57.2693</v>
+      </c>
+      <c r="U150" s="32" t="n">
+        <v>57.2693</v>
+      </c>
+      <c r="V150" s="32" t="n">
+        <v>34.4722</v>
+      </c>
+      <c r="W150" s="32" t="n">
+        <v>35.0519</v>
+      </c>
+      <c r="X150" s="32" t="n">
+        <v>37.7742</v>
+      </c>
+      <c r="Y150" s="32" t="n">
+        <v>38.6492</v>
+      </c>
+      <c r="Z150" s="32" t="n">
+        <v>48.0735</v>
+      </c>
+      <c r="AA150" s="32" t="n">
+        <v>49.6992</v>
+      </c>
+      <c r="AB150" s="32" t="n">
+        <v>48.9487</v>
+      </c>
+      <c r="AC150" s="33" t="n">
+        <v>49.2507</v>
+      </c>
     </row>
     <row r="151" ht="15" customHeight="1">
       <c r="Q151" s="27" t="n"/>
@@ -5353,13 +6397,27 @@
           <t>Mass flow rate (kgda/s)</t>
         </is>
       </c>
-      <c r="S151" s="94" t="n"/>
-      <c r="T151" s="39" t="n"/>
-      <c r="U151" s="39" t="n"/>
-      <c r="V151" s="39" t="n"/>
-      <c r="W151" s="39" t="n"/>
-      <c r="X151" s="39" t="n"/>
-      <c r="Y151" s="39" t="n"/>
+      <c r="S151" s="94" t="n">
+        <v>0.285082</v>
+      </c>
+      <c r="T151" s="39" t="n">
+        <v>0.73627</v>
+      </c>
+      <c r="U151" s="39" t="n">
+        <v>0.73627</v>
+      </c>
+      <c r="V151" s="39" t="n">
+        <v>0.7388980000000001</v>
+      </c>
+      <c r="W151" s="39" t="n">
+        <v>0.7388980000000001</v>
+      </c>
+      <c r="X151" s="39" t="n">
+        <v>0.341098</v>
+      </c>
+      <c r="Y151" s="39" t="n">
+        <v>0.397898</v>
+      </c>
       <c r="Z151" s="39" t="inlineStr">
         <is>
           <t>n/a*</t>
@@ -5370,8 +6428,12 @@
           <t>n/a*</t>
         </is>
       </c>
-      <c r="AB151" s="39" t="n"/>
-      <c r="AC151" s="40" t="n"/>
+      <c r="AB151" s="39" t="n">
+        <v>0.451143</v>
+      </c>
+      <c r="AC151" s="40" t="n">
+        <v>0.451143</v>
+      </c>
     </row>
     <row r="152" ht="15" customHeight="1">
       <c r="Q152" s="89" t="inlineStr">
@@ -5384,17 +6446,39 @@
           <t>Dry bulb temperature (°C)</t>
         </is>
       </c>
-      <c r="S152" s="92" t="n"/>
-      <c r="T152" s="28" t="n"/>
-      <c r="U152" s="28" t="n"/>
-      <c r="V152" s="28" t="n"/>
-      <c r="W152" s="28" t="n"/>
-      <c r="X152" s="28" t="n"/>
-      <c r="Y152" s="28" t="n"/>
-      <c r="Z152" s="28" t="n"/>
-      <c r="AA152" s="28" t="n"/>
-      <c r="AB152" s="28" t="n"/>
-      <c r="AC152" s="29" t="n"/>
+      <c r="S152" s="92" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="T152" s="28" t="n">
+        <v>24.4345</v>
+      </c>
+      <c r="U152" s="28" t="n">
+        <v>24.4345</v>
+      </c>
+      <c r="V152" s="28" t="n">
+        <v>12.1907</v>
+      </c>
+      <c r="W152" s="28" t="n">
+        <v>12.7531</v>
+      </c>
+      <c r="X152" s="28" t="n">
+        <v>19.0646</v>
+      </c>
+      <c r="Y152" s="28" t="n">
+        <v>18.6054</v>
+      </c>
+      <c r="Z152" s="28" t="n">
+        <v>23.2528</v>
+      </c>
+      <c r="AA152" s="28" t="n">
+        <v>24.3496</v>
+      </c>
+      <c r="AB152" s="28" t="n">
+        <v>23.8434</v>
+      </c>
+      <c r="AC152" s="29" t="n">
+        <v>24.1384</v>
+      </c>
     </row>
     <row r="153" ht="15" customHeight="1">
       <c r="Q153" s="16" t="n"/>
@@ -5403,17 +6487,39 @@
           <t>Humidity ratio (g/gda)</t>
         </is>
       </c>
-      <c r="S153" s="93" t="n"/>
-      <c r="T153" s="32" t="n"/>
-      <c r="U153" s="32" t="n"/>
-      <c r="V153" s="32" t="n"/>
-      <c r="W153" s="32" t="n"/>
-      <c r="X153" s="32" t="n"/>
-      <c r="Y153" s="32" t="n"/>
-      <c r="Z153" s="32" t="n"/>
-      <c r="AA153" s="32" t="n"/>
-      <c r="AB153" s="32" t="n"/>
-      <c r="AC153" s="33" t="n"/>
+      <c r="S153" s="93" t="n">
+        <v>0.004579</v>
+      </c>
+      <c r="T153" s="32" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="U153" s="32" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="V153" s="32" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="W153" s="32" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="X153" s="32" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="Y153" s="32" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="Z153" s="32" t="n">
+        <v>0.0064</v>
+      </c>
+      <c r="AA153" s="32" t="n">
+        <v>0.0066</v>
+      </c>
+      <c r="AB153" s="32" t="n">
+        <v>0.006508</v>
+      </c>
+      <c r="AC153" s="33" t="n">
+        <v>0.006508</v>
+      </c>
     </row>
     <row r="154" ht="15" customHeight="1">
       <c r="Q154" s="16" t="n"/>
@@ -5422,17 +6528,39 @@
           <t>Specific volume (L/kgda)</t>
         </is>
       </c>
-      <c r="S154" s="93" t="n"/>
-      <c r="T154" s="32" t="n"/>
-      <c r="U154" s="32" t="n"/>
-      <c r="V154" s="32" t="n"/>
-      <c r="W154" s="32" t="n"/>
-      <c r="X154" s="32" t="n"/>
-      <c r="Y154" s="32" t="n"/>
-      <c r="Z154" s="32" t="n"/>
-      <c r="AA154" s="32" t="n"/>
-      <c r="AB154" s="32" t="n"/>
-      <c r="AC154" s="33" t="n"/>
+      <c r="S154" s="93" t="n">
+        <v>850.5575</v>
+      </c>
+      <c r="T154" s="32" t="n">
+        <v>850.7486</v>
+      </c>
+      <c r="U154" s="32" t="n">
+        <v>850.7486</v>
+      </c>
+      <c r="V154" s="32" t="n">
+        <v>815.7454</v>
+      </c>
+      <c r="W154" s="32" t="n">
+        <v>817.3532</v>
+      </c>
+      <c r="X154" s="32" t="n">
+        <v>835.3969</v>
+      </c>
+      <c r="Y154" s="32" t="n">
+        <v>834.0841</v>
+      </c>
+      <c r="Z154" s="32" t="n">
+        <v>848.3153</v>
+      </c>
+      <c r="AA154" s="32" t="n">
+        <v>851.7254</v>
+      </c>
+      <c r="AB154" s="32" t="n">
+        <v>850.1512</v>
+      </c>
+      <c r="AC154" s="33" t="n">
+        <v>850.9956</v>
+      </c>
     </row>
     <row r="155" ht="15" customHeight="1">
       <c r="Q155" s="16" t="n"/>
@@ -5441,17 +6569,39 @@
           <t>Enthalpy (J/gda)</t>
         </is>
       </c>
-      <c r="S155" s="93" t="n"/>
-      <c r="T155" s="32" t="n"/>
-      <c r="U155" s="32" t="n"/>
-      <c r="V155" s="32" t="n"/>
-      <c r="W155" s="32" t="n"/>
-      <c r="X155" s="32" t="n"/>
-      <c r="Y155" s="32" t="n"/>
-      <c r="Z155" s="32" t="n"/>
-      <c r="AA155" s="32" t="n"/>
-      <c r="AB155" s="32" t="n"/>
-      <c r="AC155" s="33" t="n"/>
+      <c r="S155" s="93" t="n">
+        <v>36.7136</v>
+      </c>
+      <c r="T155" s="32" t="n">
+        <v>39.0959</v>
+      </c>
+      <c r="U155" s="32" t="n">
+        <v>39.0959</v>
+      </c>
+      <c r="V155" s="32" t="n">
+        <v>26.6488</v>
+      </c>
+      <c r="W155" s="32" t="n">
+        <v>27.2205</v>
+      </c>
+      <c r="X155" s="32" t="n">
+        <v>33.6368</v>
+      </c>
+      <c r="Y155" s="32" t="n">
+        <v>33.17</v>
+      </c>
+      <c r="Z155" s="32" t="n">
+        <v>39.6755</v>
+      </c>
+      <c r="AA155" s="32" t="n">
+        <v>41.3012</v>
+      </c>
+      <c r="AB155" s="32" t="n">
+        <v>40.5507</v>
+      </c>
+      <c r="AC155" s="33" t="n">
+        <v>40.8511</v>
+      </c>
     </row>
     <row r="156" ht="15" customHeight="1">
       <c r="Q156" s="27" t="n"/>
@@ -5460,13 +6610,27 @@
           <t>Mass flow rate (kgda/s)</t>
         </is>
       </c>
-      <c r="S156" s="94" t="n"/>
-      <c r="T156" s="39" t="n"/>
-      <c r="U156" s="39" t="n"/>
-      <c r="V156" s="39" t="n"/>
-      <c r="W156" s="39" t="n"/>
-      <c r="X156" s="39" t="n"/>
-      <c r="Y156" s="39" t="n"/>
+      <c r="S156" s="94" t="n">
+        <v>0.28851</v>
+      </c>
+      <c r="T156" s="39" t="n">
+        <v>0.741175</v>
+      </c>
+      <c r="U156" s="39" t="n">
+        <v>0.741175</v>
+      </c>
+      <c r="V156" s="39" t="n">
+        <v>0.741175</v>
+      </c>
+      <c r="W156" s="39" t="n">
+        <v>0.741175</v>
+      </c>
+      <c r="X156" s="39" t="n">
+        <v>0.34215</v>
+      </c>
+      <c r="Y156" s="39" t="n">
+        <v>0.399125</v>
+      </c>
       <c r="Z156" s="39" t="inlineStr">
         <is>
           <t>n/a*</t>
@@ -5477,8 +6641,12 @@
           <t>n/a*</t>
         </is>
       </c>
-      <c r="AB156" s="39" t="n"/>
-      <c r="AC156" s="40" t="n"/>
+      <c r="AB156" s="39" t="n">
+        <v>0.452623</v>
+      </c>
+      <c r="AC156" s="40" t="n">
+        <v>0.452623</v>
+      </c>
     </row>
     <row r="157" ht="15" customHeight="1">
       <c r="Q157" s="89" t="inlineStr">
@@ -5491,17 +6659,39 @@
           <t>Dry bulb temperature (°C)</t>
         </is>
       </c>
-      <c r="S157" s="92" t="n"/>
-      <c r="T157" s="28" t="n"/>
-      <c r="U157" s="28" t="n"/>
-      <c r="V157" s="28" t="n"/>
-      <c r="W157" s="28" t="n"/>
-      <c r="X157" s="28" t="n"/>
-      <c r="Y157" s="28" t="n"/>
-      <c r="Z157" s="28" t="n"/>
-      <c r="AA157" s="28" t="n"/>
-      <c r="AB157" s="28" t="n"/>
-      <c r="AC157" s="29" t="n"/>
+      <c r="S157" s="92" t="n">
+        <v>23</v>
+      </c>
+      <c r="T157" s="28" t="n">
+        <v>23.6647</v>
+      </c>
+      <c r="U157" s="28" t="n">
+        <v>23.6647</v>
+      </c>
+      <c r="V157" s="28" t="n">
+        <v>12.1907</v>
+      </c>
+      <c r="W157" s="28" t="n">
+        <v>12.7577</v>
+      </c>
+      <c r="X157" s="28" t="n">
+        <v>19.0421</v>
+      </c>
+      <c r="Y157" s="28" t="n">
+        <v>18.5852</v>
+      </c>
+      <c r="Z157" s="28" t="n">
+        <v>23.2063</v>
+      </c>
+      <c r="AA157" s="28" t="n">
+        <v>24.2965</v>
+      </c>
+      <c r="AB157" s="28" t="n">
+        <v>23.7933</v>
+      </c>
+      <c r="AC157" s="29" t="n">
+        <v>24.0883</v>
+      </c>
     </row>
     <row r="158" ht="15" customHeight="1">
       <c r="Q158" s="16" t="n"/>
@@ -5510,17 +6700,39 @@
           <t>Humidity ratio (g/gda)</t>
         </is>
       </c>
-      <c r="S158" s="93" t="n"/>
-      <c r="T158" s="32" t="n"/>
-      <c r="U158" s="32" t="n"/>
-      <c r="V158" s="32" t="n"/>
-      <c r="W158" s="32" t="n"/>
-      <c r="X158" s="32" t="n"/>
-      <c r="Y158" s="32" t="n"/>
-      <c r="Z158" s="32" t="n"/>
-      <c r="AA158" s="32" t="n"/>
-      <c r="AB158" s="32" t="n"/>
-      <c r="AC158" s="33" t="n"/>
+      <c r="S158" s="93" t="n">
+        <v>0.015743</v>
+      </c>
+      <c r="T158" s="32" t="n">
+        <v>0.0119</v>
+      </c>
+      <c r="U158" s="32" t="n">
+        <v>0.0119</v>
+      </c>
+      <c r="V158" s="32" t="n">
+        <v>0.008800000000000001</v>
+      </c>
+      <c r="W158" s="32" t="n">
+        <v>0.008800000000000001</v>
+      </c>
+      <c r="X158" s="32" t="n">
+        <v>0.008800000000000001</v>
+      </c>
+      <c r="Y158" s="32" t="n">
+        <v>0.008800000000000001</v>
+      </c>
+      <c r="Z158" s="32" t="n">
+        <v>0.0095</v>
+      </c>
+      <c r="AA158" s="32" t="n">
+        <v>0.0097</v>
+      </c>
+      <c r="AB158" s="32" t="n">
+        <v>0.009608</v>
+      </c>
+      <c r="AC158" s="33" t="n">
+        <v>0.009608</v>
+      </c>
     </row>
     <row r="159" ht="15" customHeight="1">
       <c r="Q159" s="16" t="n"/>
@@ -5529,17 +6741,39 @@
           <t>Specific volume (L/kgda)</t>
         </is>
       </c>
-      <c r="S159" s="93" t="n"/>
-      <c r="T159" s="32" t="n"/>
-      <c r="U159" s="32" t="n"/>
-      <c r="V159" s="32" t="n"/>
-      <c r="W159" s="32" t="n"/>
-      <c r="X159" s="32" t="n"/>
-      <c r="Y159" s="32" t="n"/>
-      <c r="Z159" s="32" t="n"/>
-      <c r="AA159" s="32" t="n"/>
-      <c r="AB159" s="32" t="n"/>
-      <c r="AC159" s="33" t="n"/>
+      <c r="S159" s="93" t="n">
+        <v>860.1948</v>
+      </c>
+      <c r="T159" s="32" t="n">
+        <v>856.9299999999999</v>
+      </c>
+      <c r="U159" s="32" t="n">
+        <v>856.9299999999999</v>
+      </c>
+      <c r="V159" s="32" t="n">
+        <v>819.7745</v>
+      </c>
+      <c r="W159" s="32" t="n">
+        <v>821.4034</v>
+      </c>
+      <c r="X159" s="32" t="n">
+        <v>839.4583</v>
+      </c>
+      <c r="Y159" s="32" t="n">
+        <v>838.1457</v>
+      </c>
+      <c r="Z159" s="32" t="n">
+        <v>852.3668</v>
+      </c>
+      <c r="AA159" s="32" t="n">
+        <v>855.7734</v>
+      </c>
+      <c r="AB159" s="32" t="n">
+        <v>854.2008</v>
+      </c>
+      <c r="AC159" s="33" t="n">
+        <v>855.0494</v>
+      </c>
     </row>
     <row r="160" ht="15" customHeight="1">
       <c r="Q160" s="16" t="n"/>
@@ -5548,17 +6782,39 @@
           <t>Enthalpy (J/gda)</t>
         </is>
       </c>
-      <c r="S160" s="93" t="n"/>
-      <c r="T160" s="32" t="n"/>
-      <c r="U160" s="32" t="n"/>
-      <c r="V160" s="32" t="n"/>
-      <c r="W160" s="32" t="n"/>
-      <c r="X160" s="32" t="n"/>
-      <c r="Y160" s="32" t="n"/>
-      <c r="Z160" s="32" t="n"/>
-      <c r="AA160" s="32" t="n"/>
-      <c r="AB160" s="32" t="n"/>
-      <c r="AC160" s="33" t="n"/>
+      <c r="S160" s="93" t="n">
+        <v>63.1847</v>
+      </c>
+      <c r="T160" s="32" t="n">
+        <v>54.0924</v>
+      </c>
+      <c r="U160" s="32" t="n">
+        <v>54.0924</v>
+      </c>
+      <c r="V160" s="32" t="n">
+        <v>34.4722</v>
+      </c>
+      <c r="W160" s="32" t="n">
+        <v>35.0519</v>
+      </c>
+      <c r="X160" s="32" t="n">
+        <v>41.4768</v>
+      </c>
+      <c r="Y160" s="32" t="n">
+        <v>41.0097</v>
+      </c>
+      <c r="Z160" s="32" t="n">
+        <v>47.5151</v>
+      </c>
+      <c r="AA160" s="32" t="n">
+        <v>49.1403</v>
+      </c>
+      <c r="AB160" s="32" t="n">
+        <v>48.3901</v>
+      </c>
+      <c r="AC160" s="33" t="n">
+        <v>48.6921</v>
+      </c>
     </row>
     <row r="161" ht="15" customHeight="1">
       <c r="Q161" s="27" t="n"/>
@@ -5567,13 +6823,27 @@
           <t>Mass flow rate (kgda/s)</t>
         </is>
       </c>
-      <c r="S161" s="94" t="n"/>
-      <c r="T161" s="39" t="n"/>
-      <c r="U161" s="39" t="n"/>
-      <c r="V161" s="39" t="n"/>
-      <c r="W161" s="39" t="n"/>
-      <c r="X161" s="39" t="n"/>
-      <c r="Y161" s="39" t="n"/>
+      <c r="S161" s="94" t="n">
+        <v>0.285635</v>
+      </c>
+      <c r="T161" s="39" t="n">
+        <v>0.736634</v>
+      </c>
+      <c r="U161" s="39" t="n">
+        <v>0.736634</v>
+      </c>
+      <c r="V161" s="39" t="n">
+        <v>0.7388980000000001</v>
+      </c>
+      <c r="W161" s="39" t="n">
+        <v>0.7388980000000001</v>
+      </c>
+      <c r="X161" s="39" t="n">
+        <v>0.341098</v>
+      </c>
+      <c r="Y161" s="39" t="n">
+        <v>0.397898</v>
+      </c>
       <c r="Z161" s="39" t="inlineStr">
         <is>
           <t>n/a*</t>
@@ -5584,8 +6854,12 @@
           <t>n/a*</t>
         </is>
       </c>
-      <c r="AB161" s="39" t="n"/>
-      <c r="AC161" s="40" t="n"/>
+      <c r="AB161" s="39" t="n">
+        <v>0.450936</v>
+      </c>
+      <c r="AC161" s="40" t="n">
+        <v>0.450936</v>
+      </c>
     </row>
     <row r="162" ht="15" customHeight="1">
       <c r="Q162" s="89" t="inlineStr">
@@ -5598,17 +6872,39 @@
           <t>Dry bulb temperature (°C)</t>
         </is>
       </c>
-      <c r="S162" s="92" t="n"/>
-      <c r="T162" s="28" t="n"/>
-      <c r="U162" s="28" t="n"/>
-      <c r="V162" s="28" t="n"/>
-      <c r="W162" s="28" t="n"/>
-      <c r="X162" s="28" t="n"/>
-      <c r="Y162" s="28" t="n"/>
-      <c r="Z162" s="28" t="n"/>
-      <c r="AA162" s="28" t="n"/>
-      <c r="AB162" s="28" t="n"/>
-      <c r="AC162" s="29" t="n"/>
+      <c r="S162" s="92" t="n">
+        <v>23</v>
+      </c>
+      <c r="T162" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="U162" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="V162" s="28" t="n">
+        <v>12.1907</v>
+      </c>
+      <c r="W162" s="28" t="n">
+        <v>12.7577</v>
+      </c>
+      <c r="X162" s="28" t="n">
+        <v>19.0421</v>
+      </c>
+      <c r="Y162" s="28" t="n">
+        <v>18.5852</v>
+      </c>
+      <c r="Z162" s="28" t="n">
+        <v>23.2063</v>
+      </c>
+      <c r="AA162" s="28" t="n">
+        <v>24.2965</v>
+      </c>
+      <c r="AB162" s="28" t="n">
+        <v>23.7933</v>
+      </c>
+      <c r="AC162" s="29" t="n">
+        <v>24.0883</v>
+      </c>
     </row>
     <row r="163" ht="15" customHeight="1">
       <c r="Q163" s="16" t="n"/>
@@ -5617,17 +6913,39 @@
           <t>Humidity ratio (g/gda)</t>
         </is>
       </c>
-      <c r="S163" s="93" t="n"/>
-      <c r="T163" s="32" t="n"/>
-      <c r="U163" s="32" t="n"/>
-      <c r="V163" s="32" t="n"/>
-      <c r="W163" s="32" t="n"/>
-      <c r="X163" s="32" t="n"/>
-      <c r="Y163" s="32" t="n"/>
-      <c r="Z163" s="32" t="n"/>
-      <c r="AA163" s="32" t="n"/>
-      <c r="AB163" s="32" t="n"/>
-      <c r="AC163" s="33" t="n"/>
+      <c r="S163" s="93" t="n">
+        <v>0.015743</v>
+      </c>
+      <c r="T163" s="32" t="n">
+        <v>0.0156</v>
+      </c>
+      <c r="U163" s="32" t="n">
+        <v>0.0156</v>
+      </c>
+      <c r="V163" s="32" t="n">
+        <v>0.008800000000000001</v>
+      </c>
+      <c r="W163" s="32" t="n">
+        <v>0.008800000000000001</v>
+      </c>
+      <c r="X163" s="32" t="n">
+        <v>0.008800000000000001</v>
+      </c>
+      <c r="Y163" s="32" t="n">
+        <v>0.008800000000000001</v>
+      </c>
+      <c r="Z163" s="32" t="n">
+        <v>0.0095</v>
+      </c>
+      <c r="AA163" s="32" t="n">
+        <v>0.0097</v>
+      </c>
+      <c r="AB163" s="32" t="n">
+        <v>0.009608</v>
+      </c>
+      <c r="AC163" s="33" t="n">
+        <v>0.009608</v>
+      </c>
     </row>
     <row r="164" ht="15" customHeight="1">
       <c r="Q164" s="16" t="n"/>
@@ -5636,17 +6954,39 @@
           <t>Specific volume (L/kgda)</t>
         </is>
       </c>
-      <c r="S164" s="93" t="n"/>
-      <c r="T164" s="32" t="n"/>
-      <c r="U164" s="32" t="n"/>
-      <c r="V164" s="32" t="n"/>
-      <c r="W164" s="32" t="n"/>
-      <c r="X164" s="32" t="n"/>
-      <c r="Y164" s="32" t="n"/>
-      <c r="Z164" s="32" t="n"/>
-      <c r="AA164" s="32" t="n"/>
-      <c r="AB164" s="32" t="n"/>
-      <c r="AC164" s="33" t="n"/>
+      <c r="S164" s="93" t="n">
+        <v>860.1948</v>
+      </c>
+      <c r="T164" s="32" t="n">
+        <v>860.0019</v>
+      </c>
+      <c r="U164" s="32" t="n">
+        <v>860.0019</v>
+      </c>
+      <c r="V164" s="32" t="n">
+        <v>819.7745</v>
+      </c>
+      <c r="W164" s="32" t="n">
+        <v>821.4034</v>
+      </c>
+      <c r="X164" s="32" t="n">
+        <v>839.4583</v>
+      </c>
+      <c r="Y164" s="32" t="n">
+        <v>838.1457</v>
+      </c>
+      <c r="Z164" s="32" t="n">
+        <v>852.3668</v>
+      </c>
+      <c r="AA164" s="32" t="n">
+        <v>855.7734</v>
+      </c>
+      <c r="AB164" s="32" t="n">
+        <v>854.2008</v>
+      </c>
+      <c r="AC164" s="33" t="n">
+        <v>855.0494</v>
+      </c>
     </row>
     <row r="165" ht="15" customHeight="1">
       <c r="Q165" s="16" t="n"/>
@@ -5655,17 +6995,39 @@
           <t>Enthalpy (J/gda)</t>
         </is>
       </c>
-      <c r="S165" s="93" t="n"/>
-      <c r="T165" s="32" t="n"/>
-      <c r="U165" s="32" t="n"/>
-      <c r="V165" s="32" t="n"/>
-      <c r="W165" s="32" t="n"/>
-      <c r="X165" s="32" t="n"/>
-      <c r="Y165" s="32" t="n"/>
-      <c r="Z165" s="32" t="n"/>
-      <c r="AA165" s="32" t="n"/>
-      <c r="AB165" s="32" t="n"/>
-      <c r="AC165" s="33" t="n"/>
+      <c r="S165" s="93" t="n">
+        <v>63.1847</v>
+      </c>
+      <c r="T165" s="32" t="n">
+        <v>62.821</v>
+      </c>
+      <c r="U165" s="32" t="n">
+        <v>62.821</v>
+      </c>
+      <c r="V165" s="32" t="n">
+        <v>34.4722</v>
+      </c>
+      <c r="W165" s="32" t="n">
+        <v>35.0519</v>
+      </c>
+      <c r="X165" s="32" t="n">
+        <v>41.4768</v>
+      </c>
+      <c r="Y165" s="32" t="n">
+        <v>41.0097</v>
+      </c>
+      <c r="Z165" s="32" t="n">
+        <v>47.5151</v>
+      </c>
+      <c r="AA165" s="32" t="n">
+        <v>49.1403</v>
+      </c>
+      <c r="AB165" s="32" t="n">
+        <v>48.3901</v>
+      </c>
+      <c r="AC165" s="33" t="n">
+        <v>48.6921</v>
+      </c>
     </row>
     <row r="166" ht="15" customHeight="1">
       <c r="Q166" s="27" t="n"/>
@@ -5674,13 +7036,27 @@
           <t>Mass flow rate (kgda/s)</t>
         </is>
       </c>
-      <c r="S166" s="94" t="n"/>
-      <c r="T166" s="39" t="n"/>
-      <c r="U166" s="39" t="n"/>
-      <c r="V166" s="39" t="n"/>
-      <c r="W166" s="39" t="n"/>
-      <c r="X166" s="39" t="n"/>
-      <c r="Y166" s="39" t="n"/>
+      <c r="S166" s="94" t="n">
+        <v>0.733847</v>
+      </c>
+      <c r="T166" s="39" t="n">
+        <v>0.73395</v>
+      </c>
+      <c r="U166" s="39" t="n">
+        <v>0.73395</v>
+      </c>
+      <c r="V166" s="39" t="n">
+        <v>0.7388980000000001</v>
+      </c>
+      <c r="W166" s="39" t="n">
+        <v>0.7388980000000001</v>
+      </c>
+      <c r="X166" s="39" t="n">
+        <v>0.341098</v>
+      </c>
+      <c r="Y166" s="39" t="n">
+        <v>0.397898</v>
+      </c>
       <c r="Z166" s="39" t="inlineStr">
         <is>
           <t>n/a*</t>
@@ -5691,8 +7067,12 @@
           <t>n/a*</t>
         </is>
       </c>
-      <c r="AB166" s="39" t="n"/>
-      <c r="AC166" s="40" t="n"/>
+      <c r="AB166" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC166" s="40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="167" ht="15" customHeight="1">
       <c r="Q167" s="89" t="inlineStr">
@@ -5705,17 +7085,39 @@
           <t>Dry bulb temperature (°C)</t>
         </is>
       </c>
-      <c r="S167" s="92" t="n"/>
-      <c r="T167" s="28" t="n"/>
-      <c r="U167" s="28" t="n"/>
-      <c r="V167" s="28" t="n"/>
-      <c r="W167" s="28" t="n"/>
-      <c r="X167" s="28" t="n"/>
-      <c r="Y167" s="28" t="n"/>
-      <c r="Z167" s="28" t="n"/>
-      <c r="AA167" s="28" t="n"/>
-      <c r="AB167" s="28" t="n"/>
-      <c r="AC167" s="29" t="n"/>
+      <c r="S167" s="92" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="T167" s="28" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="U167" s="28" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="V167" s="28" t="n">
+        <v>12.1907</v>
+      </c>
+      <c r="W167" s="28" t="n">
+        <v>12.7513</v>
+      </c>
+      <c r="X167" s="28" t="n">
+        <v>19.0735</v>
+      </c>
+      <c r="Y167" s="28" t="n">
+        <v>18.6133</v>
+      </c>
+      <c r="Z167" s="28" t="n">
+        <v>23.271</v>
+      </c>
+      <c r="AA167" s="28" t="n">
+        <v>24.3704</v>
+      </c>
+      <c r="AB167" s="28" t="n">
+        <v>23.863</v>
+      </c>
+      <c r="AC167" s="29" t="n">
+        <v>24.158</v>
+      </c>
     </row>
     <row r="168" ht="15" customHeight="1">
       <c r="Q168" s="16" t="n"/>
@@ -5724,17 +7126,39 @@
           <t>Humidity ratio (g/gda)</t>
         </is>
       </c>
-      <c r="S168" s="93" t="n"/>
-      <c r="T168" s="32" t="n"/>
-      <c r="U168" s="32" t="n"/>
-      <c r="V168" s="32" t="n"/>
-      <c r="W168" s="32" t="n"/>
-      <c r="X168" s="32" t="n"/>
-      <c r="Y168" s="32" t="n"/>
-      <c r="Z168" s="32" t="n"/>
-      <c r="AA168" s="32" t="n"/>
-      <c r="AB168" s="32" t="n"/>
-      <c r="AC168" s="33" t="n"/>
+      <c r="S168" s="93" t="n">
+        <v>0.004579</v>
+      </c>
+      <c r="T168" s="32" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="U168" s="32" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="V168" s="32" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="W168" s="32" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="X168" s="32" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="Y168" s="32" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="Z168" s="32" t="n">
+        <v>0.0052</v>
+      </c>
+      <c r="AA168" s="32" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="AB168" s="32" t="n">
+        <v>0.005308</v>
+      </c>
+      <c r="AC168" s="33" t="n">
+        <v>0.005308</v>
+      </c>
     </row>
     <row r="169" ht="15" customHeight="1">
       <c r="Q169" s="16" t="n"/>
@@ -5743,17 +7167,39 @@
           <t>Specific volume (L/kgda)</t>
         </is>
       </c>
-      <c r="S169" s="93" t="n"/>
-      <c r="T169" s="32" t="n"/>
-      <c r="U169" s="32" t="n"/>
-      <c r="V169" s="32" t="n"/>
-      <c r="W169" s="32" t="n"/>
-      <c r="X169" s="32" t="n"/>
-      <c r="Y169" s="32" t="n"/>
-      <c r="Z169" s="32" t="n"/>
-      <c r="AA169" s="32" t="n"/>
-      <c r="AB169" s="32" t="n"/>
-      <c r="AC169" s="33" t="n"/>
+      <c r="S169" s="93" t="n">
+        <v>850.5575</v>
+      </c>
+      <c r="T169" s="32" t="n">
+        <v>850.4503</v>
+      </c>
+      <c r="U169" s="32" t="n">
+        <v>850.4503</v>
+      </c>
+      <c r="V169" s="32" t="n">
+        <v>814.1858</v>
+      </c>
+      <c r="W169" s="32" t="n">
+        <v>815.7854</v>
+      </c>
+      <c r="X169" s="32" t="n">
+        <v>833.825</v>
+      </c>
+      <c r="Y169" s="32" t="n">
+        <v>832.5119</v>
+      </c>
+      <c r="Z169" s="32" t="n">
+        <v>846.7472</v>
+      </c>
+      <c r="AA169" s="32" t="n">
+        <v>850.1588</v>
+      </c>
+      <c r="AB169" s="32" t="n">
+        <v>848.5839</v>
+      </c>
+      <c r="AC169" s="33" t="n">
+        <v>849.4267</v>
+      </c>
     </row>
     <row r="170" ht="15" customHeight="1">
       <c r="Q170" s="16" t="n"/>
@@ -5762,17 +7208,39 @@
           <t>Enthalpy (J/gda)</t>
         </is>
       </c>
-      <c r="S170" s="93" t="n"/>
-      <c r="T170" s="32" t="n"/>
-      <c r="U170" s="32" t="n"/>
-      <c r="V170" s="32" t="n"/>
-      <c r="W170" s="32" t="n"/>
-      <c r="X170" s="32" t="n"/>
-      <c r="Y170" s="32" t="n"/>
-      <c r="Z170" s="32" t="n"/>
-      <c r="AA170" s="32" t="n"/>
-      <c r="AB170" s="32" t="n"/>
-      <c r="AC170" s="33" t="n"/>
+      <c r="S170" s="93" t="n">
+        <v>36.7136</v>
+      </c>
+      <c r="T170" s="32" t="n">
+        <v>36.5123</v>
+      </c>
+      <c r="U170" s="32" t="n">
+        <v>36.5123</v>
+      </c>
+      <c r="V170" s="32" t="n">
+        <v>23.6204</v>
+      </c>
+      <c r="W170" s="32" t="n">
+        <v>24.189</v>
+      </c>
+      <c r="X170" s="32" t="n">
+        <v>30.6021</v>
+      </c>
+      <c r="Y170" s="32" t="n">
+        <v>30.1353</v>
+      </c>
+      <c r="Z170" s="32" t="n">
+        <v>36.6409</v>
+      </c>
+      <c r="AA170" s="32" t="n">
+        <v>38.2668</v>
+      </c>
+      <c r="AB170" s="32" t="n">
+        <v>37.5162</v>
+      </c>
+      <c r="AC170" s="33" t="n">
+        <v>37.8159</v>
+      </c>
     </row>
     <row r="171" ht="15" customHeight="1">
       <c r="Q171" s="27" t="n"/>
@@ -5781,13 +7249,27 @@
           <t>Mass flow rate (kgda/s)</t>
         </is>
       </c>
-      <c r="S171" s="94" t="n"/>
-      <c r="T171" s="39" t="n"/>
-      <c r="U171" s="39" t="n"/>
-      <c r="V171" s="39" t="n"/>
-      <c r="W171" s="39" t="n"/>
-      <c r="X171" s="39" t="n"/>
-      <c r="Y171" s="39" t="n"/>
+      <c r="S171" s="94" t="n">
+        <v>0.7420020000000001</v>
+      </c>
+      <c r="T171" s="39" t="n">
+        <v>0.742061</v>
+      </c>
+      <c r="U171" s="39" t="n">
+        <v>0.742061</v>
+      </c>
+      <c r="V171" s="39" t="n">
+        <v>0.742061</v>
+      </c>
+      <c r="W171" s="39" t="n">
+        <v>0.742061</v>
+      </c>
+      <c r="X171" s="39" t="n">
+        <v>0.342558</v>
+      </c>
+      <c r="Y171" s="39" t="n">
+        <v>0.399602</v>
+      </c>
       <c r="Z171" s="39" t="inlineStr">
         <is>
           <t>n/a*</t>
@@ -5798,8 +7280,12 @@
           <t>n/a*</t>
         </is>
       </c>
-      <c r="AB171" s="39" t="n"/>
-      <c r="AC171" s="40" t="n"/>
+      <c r="AB171" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC171" s="40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="172" ht="7.5" customHeight="1"/>
     <row r="173" ht="15" customHeight="1">
@@ -6418,17 +7904,39 @@
           <t>Dry bulb temperature (°C)</t>
         </is>
       </c>
-      <c r="S185" s="92" t="n"/>
-      <c r="T185" s="28" t="n"/>
-      <c r="U185" s="28" t="n"/>
-      <c r="V185" s="28" t="n"/>
-      <c r="W185" s="28" t="n"/>
-      <c r="X185" s="28" t="n"/>
-      <c r="Y185" s="28" t="n"/>
-      <c r="Z185" s="28" t="n"/>
-      <c r="AA185" s="28" t="n"/>
-      <c r="AB185" s="28" t="n"/>
-      <c r="AC185" s="29" t="n"/>
+      <c r="S185" s="92" t="n">
+        <v>-29</v>
+      </c>
+      <c r="T185" s="28" t="n">
+        <v>-29</v>
+      </c>
+      <c r="U185" s="28" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="V185" s="28" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="W185" s="28" t="n">
+        <v>7.3892</v>
+      </c>
+      <c r="X185" s="28" t="n">
+        <v>46.4956</v>
+      </c>
+      <c r="Y185" s="28" t="n">
+        <v>35.7681</v>
+      </c>
+      <c r="Z185" s="28" t="n">
+        <v>21.1667</v>
+      </c>
+      <c r="AA185" s="28" t="n">
+        <v>22.2604</v>
+      </c>
+      <c r="AB185" s="28" t="n">
+        <v>21.8228</v>
+      </c>
+      <c r="AC185" s="29" t="n">
+        <v>22.1178</v>
+      </c>
     </row>
     <row r="186" ht="15" customHeight="1">
       <c r="B186" s="34" t="inlineStr">
@@ -6481,17 +7989,39 @@
           <t>Humidity ratio (g/gda)</t>
         </is>
       </c>
-      <c r="S186" s="93" t="n"/>
-      <c r="T186" s="32" t="n"/>
-      <c r="U186" s="32" t="n"/>
-      <c r="V186" s="32" t="n"/>
-      <c r="W186" s="32" t="n"/>
-      <c r="X186" s="32" t="n"/>
-      <c r="Y186" s="32" t="n"/>
-      <c r="Z186" s="32" t="n"/>
-      <c r="AA186" s="32" t="n"/>
-      <c r="AB186" s="32" t="n"/>
-      <c r="AC186" s="33" t="n"/>
+      <c r="S186" s="93" t="n">
+        <v>0.000259</v>
+      </c>
+      <c r="T186" s="32" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="U186" s="32" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="V186" s="32" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="W186" s="32" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="X186" s="32" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="Y186" s="32" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="Z186" s="32" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="AA186" s="32" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="AB186" s="32" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="AC186" s="33" t="n">
+        <v>0.0023</v>
+      </c>
     </row>
     <row r="187" ht="15" customHeight="1">
       <c r="B187" s="34" t="inlineStr">
@@ -6544,17 +8074,39 @@
           <t>Specific volume (L/kgda)</t>
         </is>
       </c>
-      <c r="S187" s="93" t="n"/>
-      <c r="T187" s="32" t="n"/>
-      <c r="U187" s="32" t="n"/>
-      <c r="V187" s="32" t="n"/>
-      <c r="W187" s="32" t="n"/>
-      <c r="X187" s="32" t="n"/>
-      <c r="Y187" s="32" t="n"/>
-      <c r="Z187" s="32" t="n"/>
-      <c r="AA187" s="32" t="n"/>
-      <c r="AB187" s="32" t="n"/>
-      <c r="AC187" s="33" t="n"/>
+      <c r="S187" s="93" t="n">
+        <v>691.9367</v>
+      </c>
+      <c r="T187" s="32" t="n">
+        <v>691.9823</v>
+      </c>
+      <c r="U187" s="32" t="n">
+        <v>794.6389</v>
+      </c>
+      <c r="V187" s="32" t="n">
+        <v>794.6389</v>
+      </c>
+      <c r="W187" s="32" t="n">
+        <v>795.1184</v>
+      </c>
+      <c r="X187" s="32" t="n">
+        <v>905.9558</v>
+      </c>
+      <c r="Y187" s="32" t="n">
+        <v>875.5513999999999</v>
+      </c>
+      <c r="Z187" s="32" t="n">
+        <v>836.8484999999999</v>
+      </c>
+      <c r="AA187" s="32" t="n">
+        <v>839.9583</v>
+      </c>
+      <c r="AB187" s="32" t="n">
+        <v>838.7141</v>
+      </c>
+      <c r="AC187" s="33" t="n">
+        <v>839.5529</v>
+      </c>
     </row>
     <row r="188" ht="15" customHeight="1">
       <c r="B188" s="34" t="inlineStr">
@@ -6607,17 +8159,39 @@
           <t>Enthalpy (J/gda)</t>
         </is>
       </c>
-      <c r="S188" s="93" t="n"/>
-      <c r="T188" s="32" t="n"/>
-      <c r="U188" s="32" t="n"/>
-      <c r="V188" s="32" t="n"/>
-      <c r="W188" s="32" t="n"/>
-      <c r="X188" s="32" t="n"/>
-      <c r="Y188" s="32" t="n"/>
-      <c r="Z188" s="32" t="n"/>
-      <c r="AA188" s="32" t="n"/>
-      <c r="AB188" s="32" t="n"/>
-      <c r="AC188" s="33" t="n"/>
+      <c r="S188" s="93" t="n">
+        <v>-28.5402</v>
+      </c>
+      <c r="T188" s="32" t="n">
+        <v>-28.4399</v>
+      </c>
+      <c r="U188" s="32" t="n">
+        <v>8.0176</v>
+      </c>
+      <c r="V188" s="32" t="n">
+        <v>8.0176</v>
+      </c>
+      <c r="W188" s="32" t="n">
+        <v>8.188000000000001</v>
+      </c>
+      <c r="X188" s="32" t="n">
+        <v>47.5508</v>
+      </c>
+      <c r="Y188" s="32" t="n">
+        <v>36.753</v>
+      </c>
+      <c r="Z188" s="32" t="n">
+        <v>27.1366</v>
+      </c>
+      <c r="AA188" s="32" t="n">
+        <v>28.2415</v>
+      </c>
+      <c r="AB188" s="32" t="n">
+        <v>27.7994</v>
+      </c>
+      <c r="AC188" s="33" t="n">
+        <v>28.0975</v>
+      </c>
     </row>
     <row r="189" ht="15" customHeight="1">
       <c r="B189" s="34" t="inlineStr">
@@ -6670,13 +8244,27 @@
           <t>Mass flow rate (kgda/s)</t>
         </is>
       </c>
-      <c r="S189" s="94" t="n"/>
-      <c r="T189" s="39" t="n"/>
-      <c r="U189" s="39" t="n"/>
-      <c r="V189" s="39" t="n"/>
-      <c r="W189" s="39" t="n"/>
-      <c r="X189" s="39" t="n"/>
-      <c r="Y189" s="39" t="n"/>
+      <c r="S189" s="94" t="n">
+        <v>0.286626</v>
+      </c>
+      <c r="T189" s="39" t="n">
+        <v>0.286614</v>
+      </c>
+      <c r="U189" s="39" t="n">
+        <v>0.286614</v>
+      </c>
+      <c r="V189" s="39" t="n">
+        <v>0.286614</v>
+      </c>
+      <c r="W189" s="39" t="n">
+        <v>0.286614</v>
+      </c>
+      <c r="X189" s="39" t="n">
+        <v>0.114666</v>
+      </c>
+      <c r="Y189" s="39" t="n">
+        <v>0.171948</v>
+      </c>
       <c r="Z189" s="39" t="inlineStr">
         <is>
           <t>n/a*</t>
@@ -6687,8 +8275,12 @@
           <t>n/a*</t>
         </is>
       </c>
-      <c r="AB189" s="39" t="n"/>
-      <c r="AC189" s="40" t="n"/>
+      <c r="AB189" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC189" s="40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="190" ht="15" customHeight="1">
       <c r="B190" s="34" t="inlineStr">
@@ -6745,17 +8337,39 @@
           <t>Dry bulb temperature (°C)</t>
         </is>
       </c>
-      <c r="S190" s="92" t="n"/>
-      <c r="T190" s="28" t="n"/>
-      <c r="U190" s="28" t="n"/>
-      <c r="V190" s="28" t="n"/>
-      <c r="W190" s="28" t="n"/>
-      <c r="X190" s="28" t="n"/>
-      <c r="Y190" s="28" t="n"/>
-      <c r="Z190" s="28" t="n"/>
-      <c r="AA190" s="28" t="n"/>
-      <c r="AB190" s="28" t="n"/>
-      <c r="AC190" s="29" t="n"/>
+      <c r="S190" s="92" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="T190" s="28" t="n">
+        <v>16.7133</v>
+      </c>
+      <c r="U190" s="28" t="n">
+        <v>16.7133</v>
+      </c>
+      <c r="V190" s="28" t="n">
+        <v>12.6594</v>
+      </c>
+      <c r="W190" s="28" t="n">
+        <v>12.8515</v>
+      </c>
+      <c r="X190" s="28" t="n">
+        <v>12.8515</v>
+      </c>
+      <c r="Y190" s="28" t="n">
+        <v>12.8515</v>
+      </c>
+      <c r="Z190" s="28" t="n">
+        <v>23.2853</v>
+      </c>
+      <c r="AA190" s="28" t="n">
+        <v>24.3824</v>
+      </c>
+      <c r="AB190" s="28" t="n">
+        <v>23.9342</v>
+      </c>
+      <c r="AC190" s="29" t="n">
+        <v>24.2292</v>
+      </c>
     </row>
     <row r="191" ht="15" customHeight="1">
       <c r="B191" s="36" t="inlineStr">
@@ -6808,17 +8422,39 @@
           <t>Humidity ratio (g/gda)</t>
         </is>
       </c>
-      <c r="S191" s="93" t="n"/>
-      <c r="T191" s="32" t="n"/>
-      <c r="U191" s="32" t="n"/>
-      <c r="V191" s="32" t="n"/>
-      <c r="W191" s="32" t="n"/>
-      <c r="X191" s="32" t="n"/>
-      <c r="Y191" s="32" t="n"/>
-      <c r="Z191" s="32" t="n"/>
-      <c r="AA191" s="32" t="n"/>
-      <c r="AB191" s="32" t="n"/>
-      <c r="AC191" s="33" t="n"/>
+      <c r="S191" s="93" t="n">
+        <v>0.002992</v>
+      </c>
+      <c r="T191" s="32" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="U191" s="32" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="V191" s="32" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="W191" s="32" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="X191" s="32" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="Y191" s="32" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="Z191" s="32" t="n">
+        <v>0.0049</v>
+      </c>
+      <c r="AA191" s="32" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="AB191" s="32" t="n">
+        <v>0.004959</v>
+      </c>
+      <c r="AC191" s="33" t="n">
+        <v>0.004959</v>
+      </c>
     </row>
     <row r="192" ht="15" customHeight="1">
       <c r="Q192" s="16" t="n"/>
@@ -6827,17 +8463,39 @@
           <t>Specific volume (L/kgda)</t>
         </is>
       </c>
-      <c r="S192" s="93" t="n"/>
-      <c r="T192" s="32" t="n"/>
-      <c r="U192" s="32" t="n"/>
-      <c r="V192" s="32" t="n"/>
-      <c r="W192" s="32" t="n"/>
-      <c r="X192" s="32" t="n"/>
-      <c r="Y192" s="32" t="n"/>
-      <c r="Z192" s="32" t="n"/>
-      <c r="AA192" s="32" t="n"/>
-      <c r="AB192" s="32" t="n"/>
-      <c r="AC192" s="33" t="n"/>
+      <c r="S192" s="93" t="n">
+        <v>821.6458</v>
+      </c>
+      <c r="T192" s="32" t="n">
+        <v>825.3741</v>
+      </c>
+      <c r="U192" s="32" t="n">
+        <v>825.3741</v>
+      </c>
+      <c r="V192" s="32" t="n">
+        <v>813.8308</v>
+      </c>
+      <c r="W192" s="32" t="n">
+        <v>814.3778</v>
+      </c>
+      <c r="X192" s="32" t="n">
+        <v>814.3778</v>
+      </c>
+      <c r="Y192" s="32" t="n">
+        <v>814.3778</v>
+      </c>
+      <c r="Z192" s="32" t="n">
+        <v>846.383</v>
+      </c>
+      <c r="AA192" s="32" t="n">
+        <v>849.651</v>
+      </c>
+      <c r="AB192" s="32" t="n">
+        <v>848.3157</v>
+      </c>
+      <c r="AC192" s="33" t="n">
+        <v>849.1581</v>
+      </c>
     </row>
     <row r="193" ht="15" customHeight="1">
       <c r="Q193" s="16" t="n"/>
@@ -6846,17 +8504,39 @@
           <t>Enthalpy (J/gda)</t>
         </is>
       </c>
-      <c r="S193" s="93" t="n"/>
-      <c r="T193" s="32" t="n"/>
-      <c r="U193" s="32" t="n"/>
-      <c r="V193" s="32" t="n"/>
-      <c r="W193" s="32" t="n"/>
-      <c r="X193" s="32" t="n"/>
-      <c r="Y193" s="32" t="n"/>
-      <c r="Z193" s="32" t="n"/>
-      <c r="AA193" s="32" t="n"/>
-      <c r="AB193" s="32" t="n"/>
-      <c r="AC193" s="33" t="n"/>
+      <c r="S193" s="93" t="n">
+        <v>23.1623</v>
+      </c>
+      <c r="T193" s="32" t="n">
+        <v>24.9163</v>
+      </c>
+      <c r="U193" s="32" t="n">
+        <v>24.9163</v>
+      </c>
+      <c r="V193" s="32" t="n">
+        <v>20.8139</v>
+      </c>
+      <c r="W193" s="32" t="n">
+        <v>21.0083</v>
+      </c>
+      <c r="X193" s="32" t="n">
+        <v>21.0083</v>
+      </c>
+      <c r="Y193" s="32" t="n">
+        <v>21.0083</v>
+      </c>
+      <c r="Z193" s="32" t="n">
+        <v>35.8921</v>
+      </c>
+      <c r="AA193" s="32" t="n">
+        <v>37.2605</v>
+      </c>
+      <c r="AB193" s="32" t="n">
+        <v>36.7014</v>
+      </c>
+      <c r="AC193" s="33" t="n">
+        <v>37.0009</v>
+      </c>
     </row>
     <row r="194" ht="15" customHeight="1">
       <c r="B194" s="4" t="n"/>
@@ -6866,13 +8546,27 @@
           <t>Mass flow rate (kgda/s)</t>
         </is>
       </c>
-      <c r="S194" s="94" t="n"/>
-      <c r="T194" s="39" t="n"/>
-      <c r="U194" s="39" t="n"/>
-      <c r="V194" s="39" t="n"/>
-      <c r="W194" s="39" t="n"/>
-      <c r="X194" s="39" t="n"/>
-      <c r="Y194" s="39" t="n"/>
+      <c r="S194" s="94" t="n">
+        <v>0.289465</v>
+      </c>
+      <c r="T194" s="39" t="n">
+        <v>0.336124</v>
+      </c>
+      <c r="U194" s="39" t="n">
+        <v>0.336124</v>
+      </c>
+      <c r="V194" s="39" t="n">
+        <v>0.336124</v>
+      </c>
+      <c r="W194" s="39" t="n">
+        <v>0.336124</v>
+      </c>
+      <c r="X194" s="39" t="n">
+        <v>0.138058</v>
+      </c>
+      <c r="Y194" s="39" t="n">
+        <v>0.19986</v>
+      </c>
       <c r="Z194" s="39" t="inlineStr">
         <is>
           <t>n/a*</t>
@@ -6883,8 +8577,12 @@
           <t>n/a*</t>
         </is>
       </c>
-      <c r="AB194" s="39" t="n"/>
-      <c r="AC194" s="40" t="n"/>
+      <c r="AB194" s="39" t="n">
+        <v>0.046637</v>
+      </c>
+      <c r="AC194" s="40" t="n">
+        <v>0.046637</v>
+      </c>
     </row>
     <row r="195" ht="15" customHeight="1">
       <c r="B195" s="41" t="n"/>
@@ -6898,17 +8596,39 @@
           <t>Dry bulb temperature (°C)</t>
         </is>
       </c>
-      <c r="S195" s="92" t="n"/>
-      <c r="T195" s="28" t="n"/>
-      <c r="U195" s="28" t="n"/>
-      <c r="V195" s="28" t="n"/>
-      <c r="W195" s="28" t="n"/>
-      <c r="X195" s="28" t="n"/>
-      <c r="Y195" s="28" t="n"/>
-      <c r="Z195" s="28" t="n"/>
-      <c r="AA195" s="28" t="n"/>
-      <c r="AB195" s="28" t="n"/>
-      <c r="AC195" s="29" t="n"/>
+      <c r="S195" s="92" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="T195" s="28" t="n">
+        <v>25.8369</v>
+      </c>
+      <c r="U195" s="28" t="n">
+        <v>25.8369</v>
+      </c>
+      <c r="V195" s="28" t="n">
+        <v>12.4634</v>
+      </c>
+      <c r="W195" s="28" t="n">
+        <v>12.8034</v>
+      </c>
+      <c r="X195" s="28" t="n">
+        <v>12.8034</v>
+      </c>
+      <c r="Y195" s="28" t="n">
+        <v>12.8034</v>
+      </c>
+      <c r="Z195" s="28" t="n">
+        <v>23.7535</v>
+      </c>
+      <c r="AA195" s="28" t="n">
+        <v>24.8419</v>
+      </c>
+      <c r="AB195" s="28" t="n">
+        <v>24.3213</v>
+      </c>
+      <c r="AC195" s="29" t="n">
+        <v>24.6163</v>
+      </c>
     </row>
     <row r="196" ht="15" customHeight="1">
       <c r="Q196" s="16" t="n"/>
@@ -6917,17 +8637,39 @@
           <t>Humidity ratio (g/gda)</t>
         </is>
       </c>
-      <c r="S196" s="93" t="n"/>
-      <c r="T196" s="32" t="n"/>
-      <c r="U196" s="32" t="n"/>
-      <c r="V196" s="32" t="n"/>
-      <c r="W196" s="32" t="n"/>
-      <c r="X196" s="32" t="n"/>
-      <c r="Y196" s="32" t="n"/>
-      <c r="Z196" s="32" t="n"/>
-      <c r="AA196" s="32" t="n"/>
-      <c r="AB196" s="32" t="n"/>
-      <c r="AC196" s="33" t="n"/>
+      <c r="S196" s="93" t="n">
+        <v>0.01698</v>
+      </c>
+      <c r="T196" s="32" t="n">
+        <v>0.0136</v>
+      </c>
+      <c r="U196" s="32" t="n">
+        <v>0.0136</v>
+      </c>
+      <c r="V196" s="32" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="W196" s="32" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="X196" s="32" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="Y196" s="32" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="Z196" s="32" t="n">
+        <v>0.009900000000000001</v>
+      </c>
+      <c r="AA196" s="32" t="n">
+        <v>0.0102</v>
+      </c>
+      <c r="AB196" s="32" t="n">
+        <v>0.010057</v>
+      </c>
+      <c r="AC196" s="33" t="n">
+        <v>0.010057</v>
+      </c>
     </row>
     <row r="197" ht="15" customHeight="1">
       <c r="Q197" s="16" t="n"/>
@@ -6936,17 +8678,39 @@
           <t>Specific volume (L/kgda)</t>
         </is>
       </c>
-      <c r="S197" s="93" t="n"/>
-      <c r="T197" s="32" t="n"/>
-      <c r="U197" s="32" t="n"/>
-      <c r="V197" s="32" t="n"/>
-      <c r="W197" s="32" t="n"/>
-      <c r="X197" s="32" t="n"/>
-      <c r="Y197" s="32" t="n"/>
-      <c r="Z197" s="32" t="n"/>
-      <c r="AA197" s="32" t="n"/>
-      <c r="AB197" s="32" t="n"/>
-      <c r="AC197" s="33" t="n"/>
+      <c r="S197" s="93" t="n">
+        <v>873.2133</v>
+      </c>
+      <c r="T197" s="32" t="n">
+        <v>865.5164</v>
+      </c>
+      <c r="U197" s="32" t="n">
+        <v>865.5164</v>
+      </c>
+      <c r="V197" s="32" t="n">
+        <v>820.8181</v>
+      </c>
+      <c r="W197" s="32" t="n">
+        <v>821.7952</v>
+      </c>
+      <c r="X197" s="32" t="n">
+        <v>821.7952</v>
+      </c>
+      <c r="Y197" s="32" t="n">
+        <v>821.7952</v>
+      </c>
+      <c r="Z197" s="32" t="n">
+        <v>854.4816</v>
+      </c>
+      <c r="AA197" s="32" t="n">
+        <v>858.0212</v>
+      </c>
+      <c r="AB197" s="32" t="n">
+        <v>856.3277</v>
+      </c>
+      <c r="AC197" s="33" t="n">
+        <v>857.1769</v>
+      </c>
     </row>
     <row r="198" ht="15" customHeight="1">
       <c r="Q198" s="16" t="n"/>
@@ -6955,17 +8719,39 @@
           <t>Enthalpy (J/gda)</t>
         </is>
       </c>
-      <c r="S198" s="93" t="n"/>
-      <c r="T198" s="32" t="n"/>
-      <c r="U198" s="32" t="n"/>
-      <c r="V198" s="32" t="n"/>
-      <c r="W198" s="32" t="n"/>
-      <c r="X198" s="32" t="n"/>
-      <c r="Y198" s="32" t="n"/>
-      <c r="Z198" s="32" t="n"/>
-      <c r="AA198" s="32" t="n"/>
-      <c r="AB198" s="32" t="n"/>
-      <c r="AC198" s="33" t="n"/>
+      <c r="S198" s="93" t="n">
+        <v>70.378</v>
+      </c>
+      <c r="T198" s="32" t="n">
+        <v>60.6591</v>
+      </c>
+      <c r="U198" s="32" t="n">
+        <v>60.6591</v>
+      </c>
+      <c r="V198" s="32" t="n">
+        <v>35.2558</v>
+      </c>
+      <c r="W198" s="32" t="n">
+        <v>35.6035</v>
+      </c>
+      <c r="X198" s="32" t="n">
+        <v>35.6035</v>
+      </c>
+      <c r="Y198" s="32" t="n">
+        <v>35.6035</v>
+      </c>
+      <c r="Z198" s="32" t="n">
+        <v>49.0933</v>
+      </c>
+      <c r="AA198" s="32" t="n">
+        <v>50.9725</v>
+      </c>
+      <c r="AB198" s="32" t="n">
+        <v>50.0734</v>
+      </c>
+      <c r="AC198" s="33" t="n">
+        <v>50.3757</v>
+      </c>
     </row>
     <row r="199" ht="15" customHeight="1">
       <c r="Q199" s="27" t="n"/>
@@ -6974,13 +8760,27 @@
           <t>Mass flow rate (kgda/s)</t>
         </is>
       </c>
-      <c r="S199" s="94" t="n"/>
-      <c r="T199" s="39" t="n"/>
-      <c r="U199" s="39" t="n"/>
-      <c r="V199" s="39" t="n"/>
-      <c r="W199" s="39" t="n"/>
-      <c r="X199" s="39" t="n"/>
-      <c r="Y199" s="39" t="n"/>
+      <c r="S199" s="94" t="n">
+        <v>0.287168</v>
+      </c>
+      <c r="T199" s="39" t="n">
+        <v>0.539069</v>
+      </c>
+      <c r="U199" s="39" t="n">
+        <v>0.539069</v>
+      </c>
+      <c r="V199" s="39" t="n">
+        <v>0.541526</v>
+      </c>
+      <c r="W199" s="39" t="n">
+        <v>0.541526</v>
+      </c>
+      <c r="X199" s="39" t="n">
+        <v>0.259267</v>
+      </c>
+      <c r="Y199" s="39" t="n">
+        <v>0.282755</v>
+      </c>
       <c r="Z199" s="39" t="inlineStr">
         <is>
           <t>n/a*</t>
@@ -6991,8 +8791,12 @@
           <t>n/a*</t>
         </is>
       </c>
-      <c r="AB199" s="39" t="n"/>
-      <c r="AC199" s="40" t="n"/>
+      <c r="AB199" s="39" t="n">
+        <v>0.251824</v>
+      </c>
+      <c r="AC199" s="40" t="n">
+        <v>0.251824</v>
+      </c>
     </row>
     <row r="200" ht="15" customHeight="1">
       <c r="Q200" s="89" t="inlineStr">
@@ -7005,17 +8809,39 @@
           <t>Dry bulb temperature (°C)</t>
         </is>
       </c>
-      <c r="S200" s="92" t="n"/>
-      <c r="T200" s="28" t="n"/>
-      <c r="U200" s="28" t="n"/>
-      <c r="V200" s="28" t="n"/>
-      <c r="W200" s="28" t="n"/>
-      <c r="X200" s="28" t="n"/>
-      <c r="Y200" s="28" t="n"/>
-      <c r="Z200" s="28" t="n"/>
-      <c r="AA200" s="28" t="n"/>
-      <c r="AB200" s="28" t="n"/>
-      <c r="AC200" s="29" t="n"/>
+      <c r="S200" s="92" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="T200" s="28" t="n">
+        <v>24.7959</v>
+      </c>
+      <c r="U200" s="28" t="n">
+        <v>24.7959</v>
+      </c>
+      <c r="V200" s="28" t="n">
+        <v>12.6597</v>
+      </c>
+      <c r="W200" s="28" t="n">
+        <v>12.8519</v>
+      </c>
+      <c r="X200" s="28" t="n">
+        <v>12.8519</v>
+      </c>
+      <c r="Y200" s="28" t="n">
+        <v>12.8519</v>
+      </c>
+      <c r="Z200" s="28" t="n">
+        <v>23.2682</v>
+      </c>
+      <c r="AA200" s="28" t="n">
+        <v>24.3607</v>
+      </c>
+      <c r="AB200" s="28" t="n">
+        <v>23.9146</v>
+      </c>
+      <c r="AC200" s="29" t="n">
+        <v>24.2096</v>
+      </c>
     </row>
     <row r="201" ht="15" customHeight="1">
       <c r="Q201" s="16" t="n"/>
@@ -7024,17 +8850,39 @@
           <t>Humidity ratio (g/gda)</t>
         </is>
       </c>
-      <c r="S201" s="93" t="n"/>
-      <c r="T201" s="32" t="n"/>
-      <c r="U201" s="32" t="n"/>
-      <c r="V201" s="32" t="n"/>
-      <c r="W201" s="32" t="n"/>
-      <c r="X201" s="32" t="n"/>
-      <c r="Y201" s="32" t="n"/>
-      <c r="Z201" s="32" t="n"/>
-      <c r="AA201" s="32" t="n"/>
-      <c r="AB201" s="32" t="n"/>
-      <c r="AC201" s="33" t="n"/>
+      <c r="S201" s="93" t="n">
+        <v>0.004579</v>
+      </c>
+      <c r="T201" s="32" t="n">
+        <v>0.0048</v>
+      </c>
+      <c r="U201" s="32" t="n">
+        <v>0.0048</v>
+      </c>
+      <c r="V201" s="32" t="n">
+        <v>0.0048</v>
+      </c>
+      <c r="W201" s="32" t="n">
+        <v>0.0048</v>
+      </c>
+      <c r="X201" s="32" t="n">
+        <v>0.0048</v>
+      </c>
+      <c r="Y201" s="32" t="n">
+        <v>0.0048</v>
+      </c>
+      <c r="Z201" s="32" t="n">
+        <v>0.0065</v>
+      </c>
+      <c r="AA201" s="32" t="n">
+        <v>0.0065</v>
+      </c>
+      <c r="AB201" s="32" t="n">
+        <v>0.0065</v>
+      </c>
+      <c r="AC201" s="33" t="n">
+        <v>0.0065</v>
+      </c>
     </row>
     <row r="202" ht="15" customHeight="1">
       <c r="Q202" s="16" t="n"/>
@@ -7043,17 +8891,39 @@
           <t>Specific volume (L/kgda)</t>
         </is>
       </c>
-      <c r="S202" s="93" t="n"/>
-      <c r="T202" s="32" t="n"/>
-      <c r="U202" s="32" t="n"/>
-      <c r="V202" s="32" t="n"/>
-      <c r="W202" s="32" t="n"/>
-      <c r="X202" s="32" t="n"/>
-      <c r="Y202" s="32" t="n"/>
-      <c r="Z202" s="32" t="n"/>
-      <c r="AA202" s="32" t="n"/>
-      <c r="AB202" s="32" t="n"/>
-      <c r="AC202" s="33" t="n"/>
+      <c r="S202" s="93" t="n">
+        <v>850.5575</v>
+      </c>
+      <c r="T202" s="32" t="n">
+        <v>850.5604</v>
+      </c>
+      <c r="U202" s="32" t="n">
+        <v>850.5604</v>
+      </c>
+      <c r="V202" s="32" t="n">
+        <v>815.9146</v>
+      </c>
+      <c r="W202" s="32" t="n">
+        <v>816.4633</v>
+      </c>
+      <c r="X202" s="32" t="n">
+        <v>816.4633</v>
+      </c>
+      <c r="Y202" s="32" t="n">
+        <v>816.4633</v>
+      </c>
+      <c r="Z202" s="32" t="n">
+        <v>848.4944</v>
+      </c>
+      <c r="AA202" s="32" t="n">
+        <v>851.6217</v>
+      </c>
+      <c r="AB202" s="32" t="n">
+        <v>850.3447</v>
+      </c>
+      <c r="AC202" s="33" t="n">
+        <v>851.1892</v>
+      </c>
     </row>
     <row r="203" ht="15" customHeight="1">
       <c r="Q203" s="16" t="n"/>
@@ -7062,17 +8932,39 @@
           <t>Enthalpy (J/gda)</t>
         </is>
       </c>
-      <c r="S203" s="93" t="n"/>
-      <c r="T203" s="32" t="n"/>
-      <c r="U203" s="32" t="n"/>
-      <c r="V203" s="32" t="n"/>
-      <c r="W203" s="32" t="n"/>
-      <c r="X203" s="32" t="n"/>
-      <c r="Y203" s="32" t="n"/>
-      <c r="Z203" s="32" t="n"/>
-      <c r="AA203" s="32" t="n"/>
-      <c r="AB203" s="32" t="n"/>
-      <c r="AC203" s="33" t="n"/>
+      <c r="S203" s="93" t="n">
+        <v>36.7136</v>
+      </c>
+      <c r="T203" s="32" t="n">
+        <v>37.1709</v>
+      </c>
+      <c r="U203" s="32" t="n">
+        <v>37.1709</v>
+      </c>
+      <c r="V203" s="32" t="n">
+        <v>24.8535</v>
+      </c>
+      <c r="W203" s="32" t="n">
+        <v>25.0486</v>
+      </c>
+      <c r="X203" s="32" t="n">
+        <v>25.0486</v>
+      </c>
+      <c r="Y203" s="32" t="n">
+        <v>25.0486</v>
+      </c>
+      <c r="Z203" s="32" t="n">
+        <v>39.9456</v>
+      </c>
+      <c r="AA203" s="32" t="n">
+        <v>41.0579</v>
+      </c>
+      <c r="AB203" s="32" t="n">
+        <v>40.6037</v>
+      </c>
+      <c r="AC203" s="33" t="n">
+        <v>40.9041</v>
+      </c>
     </row>
     <row r="204" ht="15" customHeight="1">
       <c r="Q204" s="27" t="n"/>
@@ -7081,13 +8973,27 @@
           <t>Mass flow rate (kgda/s)</t>
         </is>
       </c>
-      <c r="S204" s="94" t="n"/>
-      <c r="T204" s="39" t="n"/>
-      <c r="U204" s="39" t="n"/>
-      <c r="V204" s="39" t="n"/>
-      <c r="W204" s="39" t="n"/>
-      <c r="X204" s="39" t="n"/>
-      <c r="Y204" s="39" t="n"/>
+      <c r="S204" s="94" t="n">
+        <v>0.284713</v>
+      </c>
+      <c r="T204" s="39" t="n">
+        <v>0.335191</v>
+      </c>
+      <c r="U204" s="39" t="n">
+        <v>0.335191</v>
+      </c>
+      <c r="V204" s="39" t="n">
+        <v>0.335191</v>
+      </c>
+      <c r="W204" s="39" t="n">
+        <v>0.335191</v>
+      </c>
+      <c r="X204" s="39" t="n">
+        <v>0.137639</v>
+      </c>
+      <c r="Y204" s="39" t="n">
+        <v>0.199443</v>
+      </c>
       <c r="Z204" s="39" t="inlineStr">
         <is>
           <t>n/a*</t>
@@ -7098,8 +9004,12 @@
           <t>n/a*</t>
         </is>
       </c>
-      <c r="AB204" s="39" t="n"/>
-      <c r="AC204" s="40" t="n"/>
+      <c r="AB204" s="39" t="n">
+        <v>0.050456</v>
+      </c>
+      <c r="AC204" s="40" t="n">
+        <v>0.050456</v>
+      </c>
     </row>
     <row r="205" ht="15" customHeight="1">
       <c r="Q205" s="89" t="inlineStr">
@@ -7112,17 +9022,39 @@
           <t>Dry bulb temperature (°C)</t>
         </is>
       </c>
-      <c r="S205" s="92" t="n"/>
-      <c r="T205" s="28" t="n"/>
-      <c r="U205" s="28" t="n"/>
-      <c r="V205" s="28" t="n"/>
-      <c r="W205" s="28" t="n"/>
-      <c r="X205" s="28" t="n"/>
-      <c r="Y205" s="28" t="n"/>
-      <c r="Z205" s="28" t="n"/>
-      <c r="AA205" s="28" t="n"/>
-      <c r="AB205" s="28" t="n"/>
-      <c r="AC205" s="29" t="n"/>
+      <c r="S205" s="92" t="n">
+        <v>23</v>
+      </c>
+      <c r="T205" s="28" t="n">
+        <v>23.1496</v>
+      </c>
+      <c r="U205" s="28" t="n">
+        <v>23.1496</v>
+      </c>
+      <c r="V205" s="28" t="n">
+        <v>12.6604</v>
+      </c>
+      <c r="W205" s="28" t="n">
+        <v>12.853</v>
+      </c>
+      <c r="X205" s="28" t="n">
+        <v>12.853</v>
+      </c>
+      <c r="Y205" s="28" t="n">
+        <v>12.853</v>
+      </c>
+      <c r="Z205" s="28" t="n">
+        <v>23.2203</v>
+      </c>
+      <c r="AA205" s="28" t="n">
+        <v>24.2998</v>
+      </c>
+      <c r="AB205" s="28" t="n">
+        <v>23.8591</v>
+      </c>
+      <c r="AC205" s="29" t="n">
+        <v>24.1541</v>
+      </c>
     </row>
     <row r="206" ht="15" customHeight="1">
       <c r="Q206" s="16" t="n"/>
@@ -7131,17 +9063,39 @@
           <t>Humidity ratio (g/gda)</t>
         </is>
       </c>
-      <c r="S206" s="93" t="n"/>
-      <c r="T206" s="32" t="n"/>
-      <c r="U206" s="32" t="n"/>
-      <c r="V206" s="32" t="n"/>
-      <c r="W206" s="32" t="n"/>
-      <c r="X206" s="32" t="n"/>
-      <c r="Y206" s="32" t="n"/>
-      <c r="Z206" s="32" t="n"/>
-      <c r="AA206" s="32" t="n"/>
-      <c r="AB206" s="32" t="n"/>
-      <c r="AC206" s="33" t="n"/>
+      <c r="S206" s="93" t="n">
+        <v>0.015743</v>
+      </c>
+      <c r="T206" s="32" t="n">
+        <v>0.0149</v>
+      </c>
+      <c r="U206" s="32" t="n">
+        <v>0.0149</v>
+      </c>
+      <c r="V206" s="32" t="n">
+        <v>0.0091</v>
+      </c>
+      <c r="W206" s="32" t="n">
+        <v>0.0091</v>
+      </c>
+      <c r="X206" s="32" t="n">
+        <v>0.0091</v>
+      </c>
+      <c r="Y206" s="32" t="n">
+        <v>0.0091</v>
+      </c>
+      <c r="Z206" s="32" t="n">
+        <v>0.0108</v>
+      </c>
+      <c r="AA206" s="32" t="n">
+        <v>0.0109</v>
+      </c>
+      <c r="AB206" s="32" t="n">
+        <v>0.010859</v>
+      </c>
+      <c r="AC206" s="33" t="n">
+        <v>0.010859</v>
+      </c>
     </row>
     <row r="207" ht="15" customHeight="1">
       <c r="Q207" s="16" t="n"/>
@@ -7150,17 +9104,39 @@
           <t>Specific volume (L/kgda)</t>
         </is>
       </c>
-      <c r="S207" s="93" t="n"/>
-      <c r="T207" s="32" t="n"/>
-      <c r="U207" s="32" t="n"/>
-      <c r="V207" s="32" t="n"/>
-      <c r="W207" s="32" t="n"/>
-      <c r="X207" s="32" t="n"/>
-      <c r="Y207" s="32" t="n"/>
-      <c r="Z207" s="32" t="n"/>
-      <c r="AA207" s="32" t="n"/>
-      <c r="AB207" s="32" t="n"/>
-      <c r="AC207" s="33" t="n"/>
+      <c r="S207" s="93" t="n">
+        <v>860.1948</v>
+      </c>
+      <c r="T207" s="32" t="n">
+        <v>859.4915999999999</v>
+      </c>
+      <c r="U207" s="32" t="n">
+        <v>859.4915999999999</v>
+      </c>
+      <c r="V207" s="32" t="n">
+        <v>821.5145</v>
+      </c>
+      <c r="W207" s="32" t="n">
+        <v>822.068</v>
+      </c>
+      <c r="X207" s="32" t="n">
+        <v>822.068</v>
+      </c>
+      <c r="Y207" s="32" t="n">
+        <v>822.068</v>
+      </c>
+      <c r="Z207" s="32" t="n">
+        <v>854.162</v>
+      </c>
+      <c r="AA207" s="32" t="n">
+        <v>857.4087</v>
+      </c>
+      <c r="AB207" s="32" t="n">
+        <v>856.0832</v>
+      </c>
+      <c r="AC207" s="33" t="n">
+        <v>856.9335</v>
+      </c>
     </row>
     <row r="208" ht="15" customHeight="1">
       <c r="Q208" s="16" t="n"/>
@@ -7169,17 +9145,39 @@
           <t>Enthalpy (J/gda)</t>
         </is>
       </c>
-      <c r="S208" s="93" t="n"/>
-      <c r="T208" s="32" t="n"/>
-      <c r="U208" s="32" t="n"/>
-      <c r="V208" s="32" t="n"/>
-      <c r="W208" s="32" t="n"/>
-      <c r="X208" s="32" t="n"/>
-      <c r="Y208" s="32" t="n"/>
-      <c r="Z208" s="32" t="n"/>
-      <c r="AA208" s="32" t="n"/>
-      <c r="AB208" s="32" t="n"/>
-      <c r="AC208" s="33" t="n"/>
+      <c r="S208" s="93" t="n">
+        <v>63.1847</v>
+      </c>
+      <c r="T208" s="32" t="n">
+        <v>61.195</v>
+      </c>
+      <c r="U208" s="32" t="n">
+        <v>61.195</v>
+      </c>
+      <c r="V208" s="32" t="n">
+        <v>35.7098</v>
+      </c>
+      <c r="W208" s="32" t="n">
+        <v>35.9068</v>
+      </c>
+      <c r="X208" s="32" t="n">
+        <v>35.9068</v>
+      </c>
+      <c r="Y208" s="32" t="n">
+        <v>35.9068</v>
+      </c>
+      <c r="Z208" s="32" t="n">
+        <v>50.8369</v>
+      </c>
+      <c r="AA208" s="32" t="n">
+        <v>52.1992</v>
+      </c>
+      <c r="AB208" s="32" t="n">
+        <v>51.643</v>
+      </c>
+      <c r="AC208" s="33" t="n">
+        <v>51.9457</v>
+      </c>
     </row>
     <row r="209" ht="15" customHeight="1">
       <c r="Q209" s="27" t="n"/>
@@ -7188,13 +9186,27 @@
           <t>Mass flow rate (kgda/s)</t>
         </is>
       </c>
-      <c r="S209" s="94" t="n"/>
-      <c r="T209" s="39" t="n"/>
-      <c r="U209" s="39" t="n"/>
-      <c r="V209" s="39" t="n"/>
-      <c r="W209" s="39" t="n"/>
-      <c r="X209" s="39" t="n"/>
-      <c r="Y209" s="39" t="n"/>
+      <c r="S209" s="94" t="n">
+        <v>0.287743</v>
+      </c>
+      <c r="T209" s="39" t="n">
+        <v>0.33087</v>
+      </c>
+      <c r="U209" s="39" t="n">
+        <v>0.33087</v>
+      </c>
+      <c r="V209" s="39" t="n">
+        <v>0.332772</v>
+      </c>
+      <c r="W209" s="39" t="n">
+        <v>0.332772</v>
+      </c>
+      <c r="X209" s="39" t="n">
+        <v>0.136656</v>
+      </c>
+      <c r="Y209" s="39" t="n">
+        <v>0.198097</v>
+      </c>
       <c r="Z209" s="39" t="inlineStr">
         <is>
           <t>n/a*</t>
@@ -7205,8 +9217,12 @@
           <t>n/a*</t>
         </is>
       </c>
-      <c r="AB209" s="39" t="n"/>
-      <c r="AC209" s="40" t="n"/>
+      <c r="AB209" s="39" t="n">
+        <v>0.04306</v>
+      </c>
+      <c r="AC209" s="40" t="n">
+        <v>0.04306</v>
+      </c>
     </row>
     <row r="210" ht="15" customHeight="1">
       <c r="Q210" s="89" t="inlineStr">
@@ -7219,17 +9235,39 @@
           <t>Dry bulb temperature (°C)</t>
         </is>
       </c>
-      <c r="S210" s="92" t="n"/>
-      <c r="T210" s="28" t="n"/>
-      <c r="U210" s="28" t="n"/>
-      <c r="V210" s="28" t="n"/>
-      <c r="W210" s="28" t="n"/>
-      <c r="X210" s="28" t="n"/>
-      <c r="Y210" s="28" t="n"/>
-      <c r="Z210" s="28" t="n"/>
-      <c r="AA210" s="28" t="n"/>
-      <c r="AB210" s="28" t="n"/>
-      <c r="AC210" s="29" t="n"/>
+      <c r="S210" s="92" t="n">
+        <v>23</v>
+      </c>
+      <c r="T210" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="U210" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="V210" s="28" t="n">
+        <v>12.6604</v>
+      </c>
+      <c r="W210" s="28" t="n">
+        <v>12.853</v>
+      </c>
+      <c r="X210" s="28" t="n">
+        <v>12.853</v>
+      </c>
+      <c r="Y210" s="28" t="n">
+        <v>12.853</v>
+      </c>
+      <c r="Z210" s="28" t="n">
+        <v>23.2203</v>
+      </c>
+      <c r="AA210" s="28" t="n">
+        <v>24.2998</v>
+      </c>
+      <c r="AB210" s="28" t="n">
+        <v>23.8591</v>
+      </c>
+      <c r="AC210" s="29" t="n">
+        <v>24.1541</v>
+      </c>
     </row>
     <row r="211" ht="15" customHeight="1">
       <c r="Q211" s="16" t="n"/>
@@ -7238,17 +9276,39 @@
           <t>Humidity ratio (g/gda)</t>
         </is>
       </c>
-      <c r="S211" s="93" t="n"/>
-      <c r="T211" s="32" t="n"/>
-      <c r="U211" s="32" t="n"/>
-      <c r="V211" s="32" t="n"/>
-      <c r="W211" s="32" t="n"/>
-      <c r="X211" s="32" t="n"/>
-      <c r="Y211" s="32" t="n"/>
-      <c r="Z211" s="32" t="n"/>
-      <c r="AA211" s="32" t="n"/>
-      <c r="AB211" s="32" t="n"/>
-      <c r="AC211" s="33" t="n"/>
+      <c r="S211" s="93" t="n">
+        <v>0.015743</v>
+      </c>
+      <c r="T211" s="32" t="n">
+        <v>0.0156</v>
+      </c>
+      <c r="U211" s="32" t="n">
+        <v>0.0156</v>
+      </c>
+      <c r="V211" s="32" t="n">
+        <v>0.0091</v>
+      </c>
+      <c r="W211" s="32" t="n">
+        <v>0.0091</v>
+      </c>
+      <c r="X211" s="32" t="n">
+        <v>0.0091</v>
+      </c>
+      <c r="Y211" s="32" t="n">
+        <v>0.0091</v>
+      </c>
+      <c r="Z211" s="32" t="n">
+        <v>0.0108</v>
+      </c>
+      <c r="AA211" s="32" t="n">
+        <v>0.0109</v>
+      </c>
+      <c r="AB211" s="32" t="n">
+        <v>0.010859</v>
+      </c>
+      <c r="AC211" s="33" t="n">
+        <v>0.010859</v>
+      </c>
     </row>
     <row r="212" ht="15" customHeight="1">
       <c r="Q212" s="16" t="n"/>
@@ -7257,17 +9317,39 @@
           <t>Specific volume (L/kgda)</t>
         </is>
       </c>
-      <c r="S212" s="93" t="n"/>
-      <c r="T212" s="32" t="n"/>
-      <c r="U212" s="32" t="n"/>
-      <c r="V212" s="32" t="n"/>
-      <c r="W212" s="32" t="n"/>
-      <c r="X212" s="32" t="n"/>
-      <c r="Y212" s="32" t="n"/>
-      <c r="Z212" s="32" t="n"/>
-      <c r="AA212" s="32" t="n"/>
-      <c r="AB212" s="32" t="n"/>
-      <c r="AC212" s="33" t="n"/>
+      <c r="S212" s="93" t="n">
+        <v>860.1948</v>
+      </c>
+      <c r="T212" s="32" t="n">
+        <v>860.0019</v>
+      </c>
+      <c r="U212" s="32" t="n">
+        <v>860.0019</v>
+      </c>
+      <c r="V212" s="32" t="n">
+        <v>821.5145</v>
+      </c>
+      <c r="W212" s="32" t="n">
+        <v>822.068</v>
+      </c>
+      <c r="X212" s="32" t="n">
+        <v>822.068</v>
+      </c>
+      <c r="Y212" s="32" t="n">
+        <v>822.068</v>
+      </c>
+      <c r="Z212" s="32" t="n">
+        <v>854.162</v>
+      </c>
+      <c r="AA212" s="32" t="n">
+        <v>857.4087</v>
+      </c>
+      <c r="AB212" s="32" t="n">
+        <v>856.0832</v>
+      </c>
+      <c r="AC212" s="33" t="n">
+        <v>856.9335</v>
+      </c>
     </row>
     <row r="213" ht="15" customHeight="1">
       <c r="Q213" s="16" t="n"/>
@@ -7276,17 +9358,39 @@
           <t>Enthalpy (J/gda)</t>
         </is>
       </c>
-      <c r="S213" s="93" t="n"/>
-      <c r="T213" s="32" t="n"/>
-      <c r="U213" s="32" t="n"/>
-      <c r="V213" s="32" t="n"/>
-      <c r="W213" s="32" t="n"/>
-      <c r="X213" s="32" t="n"/>
-      <c r="Y213" s="32" t="n"/>
-      <c r="Z213" s="32" t="n"/>
-      <c r="AA213" s="32" t="n"/>
-      <c r="AB213" s="32" t="n"/>
-      <c r="AC213" s="33" t="n"/>
+      <c r="S213" s="93" t="n">
+        <v>63.1847</v>
+      </c>
+      <c r="T213" s="32" t="n">
+        <v>62.821</v>
+      </c>
+      <c r="U213" s="32" t="n">
+        <v>62.821</v>
+      </c>
+      <c r="V213" s="32" t="n">
+        <v>35.7098</v>
+      </c>
+      <c r="W213" s="32" t="n">
+        <v>35.9068</v>
+      </c>
+      <c r="X213" s="32" t="n">
+        <v>35.9068</v>
+      </c>
+      <c r="Y213" s="32" t="n">
+        <v>35.9068</v>
+      </c>
+      <c r="Z213" s="32" t="n">
+        <v>50.8369</v>
+      </c>
+      <c r="AA213" s="32" t="n">
+        <v>52.1992</v>
+      </c>
+      <c r="AB213" s="32" t="n">
+        <v>51.643</v>
+      </c>
+      <c r="AC213" s="33" t="n">
+        <v>51.9457</v>
+      </c>
     </row>
     <row r="214" ht="15" customHeight="1">
       <c r="Q214" s="27" t="n"/>
@@ -7295,13 +9399,27 @@
           <t>Mass flow rate (kgda/s)</t>
         </is>
       </c>
-      <c r="S214" s="94" t="n"/>
-      <c r="T214" s="39" t="n"/>
-      <c r="U214" s="39" t="n"/>
-      <c r="V214" s="39" t="n"/>
-      <c r="W214" s="39" t="n"/>
-      <c r="X214" s="39" t="n"/>
-      <c r="Y214" s="39" t="n"/>
+      <c r="S214" s="94" t="n">
+        <v>0.330595</v>
+      </c>
+      <c r="T214" s="39" t="n">
+        <v>0.330642</v>
+      </c>
+      <c r="U214" s="39" t="n">
+        <v>0.330642</v>
+      </c>
+      <c r="V214" s="39" t="n">
+        <v>0.332772</v>
+      </c>
+      <c r="W214" s="39" t="n">
+        <v>0.332772</v>
+      </c>
+      <c r="X214" s="39" t="n">
+        <v>0.136656</v>
+      </c>
+      <c r="Y214" s="39" t="n">
+        <v>0.198097</v>
+      </c>
       <c r="Z214" s="39" t="inlineStr">
         <is>
           <t>n/a*</t>
@@ -7312,8 +9430,12 @@
           <t>n/a*</t>
         </is>
       </c>
-      <c r="AB214" s="39" t="n"/>
-      <c r="AC214" s="40" t="n"/>
+      <c r="AB214" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC214" s="40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="215" ht="15" customHeight="1">
       <c r="Q215" s="89" t="inlineStr">
@@ -7326,17 +9448,39 @@
           <t>Dry bulb temperature (°C)</t>
         </is>
       </c>
-      <c r="S215" s="92" t="n"/>
-      <c r="T215" s="28" t="n"/>
-      <c r="U215" s="28" t="n"/>
-      <c r="V215" s="28" t="n"/>
-      <c r="W215" s="28" t="n"/>
-      <c r="X215" s="28" t="n"/>
-      <c r="Y215" s="28" t="n"/>
-      <c r="Z215" s="28" t="n"/>
-      <c r="AA215" s="28" t="n"/>
-      <c r="AB215" s="28" t="n"/>
-      <c r="AC215" s="29" t="n"/>
+      <c r="S215" s="92" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="T215" s="28" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="U215" s="28" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="V215" s="28" t="n">
+        <v>12.6596</v>
+      </c>
+      <c r="W215" s="28" t="n">
+        <v>12.8518</v>
+      </c>
+      <c r="X215" s="28" t="n">
+        <v>12.8518</v>
+      </c>
+      <c r="Y215" s="28" t="n">
+        <v>12.8518</v>
+      </c>
+      <c r="Z215" s="28" t="n">
+        <v>23.2712</v>
+      </c>
+      <c r="AA215" s="28" t="n">
+        <v>24.3646</v>
+      </c>
+      <c r="AB215" s="28" t="n">
+        <v>23.9181</v>
+      </c>
+      <c r="AC215" s="29" t="n">
+        <v>24.2131</v>
+      </c>
     </row>
     <row r="216" ht="15" customHeight="1">
       <c r="Q216" s="16" t="n"/>
@@ -7345,17 +9489,39 @@
           <t>Humidity ratio (g/gda)</t>
         </is>
       </c>
-      <c r="S216" s="93" t="n"/>
-      <c r="T216" s="32" t="n"/>
-      <c r="U216" s="32" t="n"/>
-      <c r="V216" s="32" t="n"/>
-      <c r="W216" s="32" t="n"/>
-      <c r="X216" s="32" t="n"/>
-      <c r="Y216" s="32" t="n"/>
-      <c r="Z216" s="32" t="n"/>
-      <c r="AA216" s="32" t="n"/>
-      <c r="AB216" s="32" t="n"/>
-      <c r="AC216" s="33" t="n"/>
+      <c r="S216" s="93" t="n">
+        <v>0.004579</v>
+      </c>
+      <c r="T216" s="32" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="U216" s="32" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="V216" s="32" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="W216" s="32" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="X216" s="32" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="Y216" s="32" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="Z216" s="32" t="n">
+        <v>0.0062</v>
+      </c>
+      <c r="AA216" s="32" t="n">
+        <v>0.0062</v>
+      </c>
+      <c r="AB216" s="32" t="n">
+        <v>0.0062</v>
+      </c>
+      <c r="AC216" s="33" t="n">
+        <v>0.0062</v>
+      </c>
     </row>
     <row r="217" ht="15" customHeight="1">
       <c r="Q217" s="16" t="n"/>
@@ -7364,17 +9530,39 @@
           <t>Specific volume (L/kgda)</t>
         </is>
       </c>
-      <c r="S217" s="93" t="n"/>
-      <c r="T217" s="32" t="n"/>
-      <c r="U217" s="32" t="n"/>
-      <c r="V217" s="32" t="n"/>
-      <c r="W217" s="32" t="n"/>
-      <c r="X217" s="32" t="n"/>
-      <c r="Y217" s="32" t="n"/>
-      <c r="Z217" s="32" t="n"/>
-      <c r="AA217" s="32" t="n"/>
-      <c r="AB217" s="32" t="n"/>
-      <c r="AC217" s="33" t="n"/>
+      <c r="S217" s="93" t="n">
+        <v>850.5575</v>
+      </c>
+      <c r="T217" s="32" t="n">
+        <v>850.4503</v>
+      </c>
+      <c r="U217" s="32" t="n">
+        <v>850.4503</v>
+      </c>
+      <c r="V217" s="32" t="n">
+        <v>815.5237</v>
+      </c>
+      <c r="W217" s="32" t="n">
+        <v>816.0722</v>
+      </c>
+      <c r="X217" s="32" t="n">
+        <v>816.0722</v>
+      </c>
+      <c r="Y217" s="32" t="n">
+        <v>816.0722</v>
+      </c>
+      <c r="Z217" s="32" t="n">
+        <v>848.098</v>
+      </c>
+      <c r="AA217" s="32" t="n">
+        <v>851.2263</v>
+      </c>
+      <c r="AB217" s="32" t="n">
+        <v>849.9489</v>
+      </c>
+      <c r="AC217" s="33" t="n">
+        <v>850.793</v>
+      </c>
     </row>
     <row r="218" ht="15" customHeight="1">
       <c r="Q218" s="16" t="n"/>
@@ -7383,17 +9571,39 @@
           <t>Enthalpy (J/gda)</t>
         </is>
       </c>
-      <c r="S218" s="93" t="n"/>
-      <c r="T218" s="32" t="n"/>
-      <c r="U218" s="32" t="n"/>
-      <c r="V218" s="32" t="n"/>
-      <c r="W218" s="32" t="n"/>
-      <c r="X218" s="32" t="n"/>
-      <c r="Y218" s="32" t="n"/>
-      <c r="Z218" s="32" t="n"/>
-      <c r="AA218" s="32" t="n"/>
-      <c r="AB218" s="32" t="n"/>
-      <c r="AC218" s="33" t="n"/>
+      <c r="S218" s="93" t="n">
+        <v>36.7136</v>
+      </c>
+      <c r="T218" s="32" t="n">
+        <v>36.5123</v>
+      </c>
+      <c r="U218" s="32" t="n">
+        <v>36.5123</v>
+      </c>
+      <c r="V218" s="32" t="n">
+        <v>24.096</v>
+      </c>
+      <c r="W218" s="32" t="n">
+        <v>24.291</v>
+      </c>
+      <c r="X218" s="32" t="n">
+        <v>24.291</v>
+      </c>
+      <c r="Y218" s="32" t="n">
+        <v>24.291</v>
+      </c>
+      <c r="Z218" s="32" t="n">
+        <v>39.1854</v>
+      </c>
+      <c r="AA218" s="32" t="n">
+        <v>40.298</v>
+      </c>
+      <c r="AB218" s="32" t="n">
+        <v>39.8437</v>
+      </c>
+      <c r="AC218" s="33" t="n">
+        <v>40.1438</v>
+      </c>
     </row>
     <row r="219" ht="15" customHeight="1">
       <c r="Q219" s="27" t="n"/>
@@ -7402,13 +9612,27 @@
           <t>Mass flow rate (kgda/s)</t>
         </is>
       </c>
-      <c r="S219" s="94" t="n"/>
-      <c r="T219" s="39" t="n"/>
-      <c r="U219" s="39" t="n"/>
-      <c r="V219" s="39" t="n"/>
-      <c r="W219" s="39" t="n"/>
-      <c r="X219" s="39" t="n"/>
-      <c r="Y219" s="39" t="n"/>
+      <c r="S219" s="94" t="n">
+        <v>0.335364</v>
+      </c>
+      <c r="T219" s="39" t="n">
+        <v>0.335391</v>
+      </c>
+      <c r="U219" s="39" t="n">
+        <v>0.335391</v>
+      </c>
+      <c r="V219" s="39" t="n">
+        <v>0.335391</v>
+      </c>
+      <c r="W219" s="39" t="n">
+        <v>0.335391</v>
+      </c>
+      <c r="X219" s="39" t="n">
+        <v>0.13768</v>
+      </c>
+      <c r="Y219" s="39" t="n">
+        <v>0.199502</v>
+      </c>
       <c r="Z219" s="39" t="inlineStr">
         <is>
           <t>n/a*</t>
@@ -7419,8 +9643,12 @@
           <t>n/a*</t>
         </is>
       </c>
-      <c r="AB219" s="39" t="n"/>
-      <c r="AC219" s="40" t="n"/>
+      <c r="AB219" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC219" s="40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="220" ht="7.5" customHeight="1"/>
     <row r="221" ht="15" customHeight="1">

--- a/140_tests/results/OpenBSE_Std140_AE_Output.xlsx
+++ b/140_tests/results/OpenBSE_Std140_AE_Output.xlsx
@@ -2188,7 +2188,7 @@
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>OpenBSE 0.6.0</t>
+          <t>OpenBSE 0.7.0</t>
         </is>
       </c>
       <c r="D50" s="7" t="n"/>
